--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -492,16 +492,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -530,16 +522,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -568,16 +552,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -601,21 +577,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -644,16 +608,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -682,16 +638,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -720,16 +668,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -758,16 +698,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -796,16 +728,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -834,16 +758,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -867,21 +783,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -910,16 +814,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -948,16 +844,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -986,16 +874,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1024,16 +904,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1062,16 +934,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1100,16 +964,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1138,16 +994,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1176,16 +1024,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1209,21 +1049,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1247,21 +1075,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1285,21 +1101,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1323,21 +1127,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1352,7 +1144,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1361,21 +1153,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1390,7 +1170,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1399,21 +1179,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1428,7 +1196,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1437,21 +1205,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1466,7 +1222,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1475,21 +1231,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1504,7 +1248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1513,21 +1257,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1542,7 +1274,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1551,21 +1283,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1580,7 +1300,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1589,21 +1309,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1627,21 +1335,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1670,16 +1366,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1708,16 +1396,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1746,16 +1426,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -1784,16 +1456,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -1822,16 +1486,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1860,16 +1516,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1898,16 +1546,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -1922,7 +1562,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1936,19 +1576,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1592,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1974,19 +1606,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2012,16 +1636,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2050,16 +1666,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2088,16 +1696,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2126,16 +1726,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2164,16 +1756,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2202,16 +1786,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2240,16 +1816,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2264,13 +1832,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2278,19 +1846,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2302,13 +1862,13 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2316,19 +1876,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2340,13 +1892,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2354,19 +1906,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2392,16 +1936,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2430,16 +1966,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2454,7 +1982,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -2463,24 +1991,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2501,21 +2017,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2530,7 +2034,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2539,21 +2043,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2568,7 +2060,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -2577,24 +2069,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2615,21 +2095,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2644,7 +2112,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2653,24 +2121,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2138,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2691,21 +2147,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2720,7 +2164,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2729,21 +2173,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -2758,7 +2190,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2767,24 +2199,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2805,21 +2225,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -2834,13 +2242,13 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2848,19 +2256,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2872,13 +2272,13 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2886,19 +2286,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2302,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2924,19 +2316,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2332,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -2962,16 +2346,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -2986,7 +2362,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -3000,19 +2376,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3038,16 +2406,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3076,16 +2436,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3114,16 +2466,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3138,7 +2482,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -3152,16 +2496,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3176,7 +2512,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -3190,16 +2526,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3214,7 +2542,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -3228,16 +2556,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3266,16 +2586,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3290,7 +2602,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -3304,16 +2616,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3328,7 +2632,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -3342,16 +2646,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3380,16 +2676,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -3404,7 +2692,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -3418,16 +2706,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3442,7 +2722,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -3456,16 +2736,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3480,7 +2752,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -3494,16 +2766,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3532,16 +2796,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3556,7 +2812,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -3570,16 +2826,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3594,7 +2842,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -3608,16 +2856,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3646,16 +2886,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3684,16 +2916,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3722,16 +2946,8 @@
           <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3746,7 +2962,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -3760,19 +2976,11 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3784,7 +2992,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -3798,19 +3006,11 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3022,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -3836,16 +3036,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -3860,7 +3052,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -3874,19 +3066,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3082,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3912,19 +3096,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3950,16 +3126,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -3974,7 +3142,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -3988,16 +3156,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4012,7 +3172,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -4026,19 +3186,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4050,7 +3202,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -4064,19 +3216,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4088,7 +3232,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -4102,19 +3246,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4126,7 +3262,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4140,16 +3276,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4164,7 +3292,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -4178,19 +3306,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4202,7 +3322,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -4216,19 +3336,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4240,7 +3352,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -4254,16 +3366,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4278,7 +3382,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -4292,16 +3396,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4316,7 +3412,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -4330,19 +3426,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4354,7 +3442,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -4368,19 +3456,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4392,7 +3472,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -4406,19 +3486,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4430,7 +3502,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -4444,16 +3516,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4482,16 +3546,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4506,7 +3562,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -4520,19 +3576,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4558,16 +3606,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4582,7 +3622,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -4596,16 +3636,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4620,7 +3652,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -4634,16 +3666,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4658,7 +3682,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -4672,19 +3696,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4696,7 +3712,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -4710,19 +3726,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4748,16 +3756,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -4781,21 +3781,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4824,16 +3812,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4857,21 +3837,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -4900,16 +3868,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -4924,7 +3884,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4933,24 +3893,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4962,7 +3910,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4971,24 +3919,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5014,16 +3950,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5052,16 +3980,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5076,7 +3996,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -5090,19 +4010,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5114,7 +4026,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -5128,19 +4040,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5166,16 +4070,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -5204,16 +4100,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5237,21 +4125,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5266,7 +4142,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -5275,21 +4151,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5304,7 +4168,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5313,21 +4177,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5351,21 +4203,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5394,16 +4234,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5432,16 +4264,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5456,7 +4280,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5470,19 +4294,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5508,16 +4324,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -5532,7 +4340,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -5546,19 +4354,11 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5570,7 +4370,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -5584,16 +4384,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5608,7 +4400,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -5622,16 +4414,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5646,7 +4430,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -5660,16 +4444,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5684,7 +4460,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -5698,16 +4474,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5722,7 +4490,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -5736,16 +4504,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5760,7 +4520,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -5774,16 +4534,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5798,7 +4550,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -5812,16 +4564,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5850,16 +4594,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -5874,7 +4610,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -5888,16 +4624,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5912,7 +4640,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -5926,16 +4654,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5950,7 +4670,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -5964,16 +4684,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -5988,7 +4700,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -6002,16 +4714,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6040,16 +4744,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6078,16 +4774,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6102,7 +4790,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -6116,16 +4804,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6140,7 +4820,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -6154,16 +4834,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6178,7 +4850,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -6192,16 +4864,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6216,7 +4880,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -6230,16 +4894,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6254,7 +4910,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -6268,19 +4924,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6292,7 +4940,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -6306,16 +4954,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6330,7 +4970,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -6344,19 +4984,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -6368,7 +5000,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -6382,16 +5014,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6406,7 +5030,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -6420,16 +5044,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6458,16 +5074,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6496,16 +5104,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6520,7 +5120,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -6534,19 +5134,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -6558,7 +5150,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -6572,19 +5164,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6610,16 +5194,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6634,7 +5210,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -6648,19 +5224,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -6672,7 +5240,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -6686,19 +5254,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -6724,16 +5284,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6762,16 +5314,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6800,16 +5344,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6838,16 +5374,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -6871,21 +5399,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -6914,16 +5430,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -6938,7 +5446,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4828870663</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -6952,19 +5460,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -6976,7 +5476,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4828853669</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -6990,19 +5490,11 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7028,16 +5520,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7066,16 +5550,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7104,16 +5580,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7142,16 +5610,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7180,16 +5640,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7218,16 +5670,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -7256,16 +5700,8 @@
           <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7294,16 +5730,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7332,16 +5760,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7356,7 +5776,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4828876907</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -7370,16 +5790,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7394,7 +5806,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4829107379</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -7408,16 +5820,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7432,7 +5836,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4829201314</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -7446,16 +5850,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7470,7 +5866,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4828903098</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -7484,19 +5880,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7508,7 +5896,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4828872529</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -7522,19 +5910,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -7560,16 +5940,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7598,16 +5970,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7636,16 +6000,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>GENERAL</t>
@@ -7674,16 +6030,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7712,16 +6060,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7750,16 +6090,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7788,16 +6120,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7826,16 +6150,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7864,16 +6180,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7902,16 +6210,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7940,16 +6240,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -7978,16 +6270,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8016,16 +6300,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8054,16 +6330,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8092,16 +6360,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8130,16 +6390,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8168,16 +6420,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8206,16 +6450,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8244,16 +6480,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8282,16 +6510,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8320,16 +6540,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8358,16 +6570,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8396,16 +6600,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8434,16 +6630,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8467,21 +6655,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8505,21 +6681,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8543,21 +6707,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8586,16 +6738,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8624,16 +6768,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8662,16 +6798,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8700,16 +6828,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8738,16 +6858,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8776,16 +6888,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8814,16 +6918,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8852,16 +6948,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8890,16 +6978,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8928,16 +7008,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8966,16 +7038,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -8990,7 +7054,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -9004,16 +7068,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9028,7 +7084,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -9042,16 +7098,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9080,16 +7128,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9113,21 +7153,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9156,16 +7184,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9189,21 +7209,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9227,21 +7235,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9270,16 +7266,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9308,16 +7296,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9346,16 +7326,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9384,16 +7356,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9422,16 +7386,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9460,16 +7416,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9498,16 +7446,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9536,16 +7476,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9574,16 +7506,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9612,16 +7536,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9650,16 +7566,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9688,16 +7596,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9726,16 +7626,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9764,16 +7656,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9802,16 +7686,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9835,21 +7711,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -9878,16 +7742,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9916,16 +7772,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9954,16 +7802,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -9992,16 +7832,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10030,16 +7862,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10068,16 +7892,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10101,21 +7917,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10144,16 +7948,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10182,16 +7978,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10220,16 +8008,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10258,16 +8038,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10296,16 +8068,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10334,16 +8098,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10372,16 +8128,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10405,21 +8153,9 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10448,16 +8184,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10486,16 +8214,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10524,16 +8244,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10562,16 +8274,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10600,16 +8304,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10638,16 +8334,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10662,7 +8350,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -10676,19 +8364,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10700,7 +8380,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -10714,19 +8394,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10752,16 +8424,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10790,16 +8454,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10828,16 +8484,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10866,16 +8514,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -10904,16 +8544,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -10928,13 +8560,13 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -10942,19 +8574,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10966,13 +8590,13 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -10980,19 +8604,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11018,16 +8634,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11051,21 +8659,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11089,21 +8685,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11127,21 +8711,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11165,21 +8737,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11208,16 +8768,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11246,16 +8798,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11284,16 +8828,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11322,16 +8858,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11360,16 +8888,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11398,16 +8918,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11436,16 +8948,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11474,16 +8978,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11498,7 +8994,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -11512,16 +9008,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11536,7 +9024,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -11550,19 +9038,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -11574,7 +9054,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -11588,16 +9068,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11612,7 +9084,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -11626,19 +9098,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11650,7 +9114,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -11664,19 +9128,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -11688,7 +9144,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -11702,16 +9158,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11726,7 +9174,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -11740,16 +9188,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11764,7 +9204,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -11778,19 +9218,11 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11802,7 +9234,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -11816,16 +9248,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11840,7 +9264,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -11854,16 +9278,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11878,7 +9294,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -11892,19 +9308,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -11916,7 +9324,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -11930,16 +9338,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -11968,16 +9368,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -11992,7 +9384,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -12006,19 +9398,11 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12030,7 +9414,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -12044,16 +9428,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12068,7 +9444,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -12082,16 +9458,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12106,7 +9474,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -12120,19 +9488,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12144,7 +9504,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -12158,19 +9518,11 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12191,21 +9543,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12234,16 +9574,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12267,21 +9599,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12310,16 +9630,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12334,7 +9646,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -12343,24 +9655,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12372,7 +9672,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -12381,24 +9681,12 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12424,16 +9712,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12462,16 +9742,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12500,16 +9772,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12538,16 +9802,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12562,7 +9818,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -12576,16 +9832,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12600,7 +9848,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829255442</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -12614,16 +9862,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12652,16 +9892,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12690,16 +9922,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12728,16 +9952,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12766,16 +9982,8 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12804,16 +10012,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12842,16 +10042,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -12866,7 +10058,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -12880,19 +10072,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -12904,7 +10088,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -12918,19 +10102,11 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -12956,16 +10132,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -12994,16 +10162,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13032,16 +10192,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13070,16 +10222,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13108,16 +10252,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13146,16 +10282,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13184,16 +10312,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13222,16 +10342,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>HIGH_INTENT_NUDGE</t>
@@ -13260,16 +10372,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
@@ -13298,16 +10402,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>GENERAL</t>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H339"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,25 +478,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -549,14 +549,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -568,21 +568,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -594,25 +598,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -624,18 +628,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -654,18 +658,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -684,18 +688,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -714,25 +718,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -744,25 +748,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -774,7 +778,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -783,7 +787,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -800,18 +808,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -890,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -908,7 +916,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -920,7 +928,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -931,7 +939,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -950,18 +958,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -980,18 +988,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1010,18 +1018,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1040,21 +1048,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1078,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1092,21 +1108,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1138,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1127,7 +1147,11 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
@@ -1144,7 +1168,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1153,7 +1177,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
@@ -1170,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1179,12 +1207,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1205,12 +1237,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1231,12 +1267,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1257,7 +1297,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
@@ -1274,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1283,7 +1327,11 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
@@ -1300,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1309,12 +1357,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1335,12 +1387,16 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1352,25 +1408,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1382,25 +1438,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1412,18 +1468,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1442,25 +1498,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1472,18 +1528,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1502,25 +1558,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4832556634</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1532,25 +1588,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1562,25 +1618,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1592,25 +1648,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1678,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>dave1102</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1633,14 +1689,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1663,14 +1719,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1738,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1712,7 +1768,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1723,14 +1779,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1798,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1753,14 +1809,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1772,25 +1828,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1802,18 +1858,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1832,25 +1888,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1862,18 +1918,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1892,25 +1948,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832771015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1978,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1933,7 +1989,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1952,25 +2008,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1982,21 +2038,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2008,16 +2068,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4833215714</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
@@ -2034,16 +2098,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
@@ -2060,21 +2128,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2086,21 +2158,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833915167</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[PF]트래픽_유사+관심사</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2112,21 +2188,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2138,21 +2218,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2164,21 +2248,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2278,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2216,16 +2308,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
@@ -2242,18 +2338,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2272,18 +2368,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4833788564</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2302,18 +2398,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2332,25 +2428,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2362,18 +2458,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2392,25 +2488,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2422,18 +2518,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2452,25 +2548,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2578,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2493,14 +2589,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2608,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jinchoi24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -2523,7 +2619,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -2542,7 +2638,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4832811973</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -2553,7 +2649,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -2572,7 +2668,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2583,14 +2679,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2698,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -2613,14 +2709,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2632,18 +2728,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -2662,25 +2758,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2692,18 +2788,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -2722,18 +2818,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -2752,18 +2848,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -2782,18 +2878,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2812,18 +2908,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -2842,18 +2938,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2872,18 +2968,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2902,18 +2998,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -2932,25 +3028,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2962,25 +3058,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2992,25 +3088,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3022,25 +3118,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3052,25 +3148,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3178,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -3100,7 +3196,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3112,25 +3208,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3142,25 +3238,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3172,25 +3268,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3202,25 +3298,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3232,13 +3328,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3262,7 +3358,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3292,7 +3388,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3322,13 +3418,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3352,7 +3448,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -3382,25 +3478,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3508,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -3430,7 +3526,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3442,25 +3538,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3472,18 +3568,18 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -3502,18 +3598,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -3532,25 +3628,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3562,25 +3658,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3592,25 +3688,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3622,25 +3718,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3652,25 +3748,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3682,25 +3778,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3712,25 +3808,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3838,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -3772,16 +3868,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
@@ -3798,18 +3898,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -3828,16 +3928,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
@@ -3854,25 +3958,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3884,21 +3988,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3910,16 +4018,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
@@ -3936,25 +4048,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3966,7 +4078,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -3977,14 +4089,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3996,25 +4108,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4026,18 +4138,18 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -4056,25 +4168,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4097,14 +4209,14 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4116,16 +4228,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
@@ -4142,21 +4258,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4168,16 +4288,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
@@ -4194,16 +4318,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
@@ -4220,18 +4348,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -4250,18 +4378,18 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -4280,25 +4408,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4310,25 +4438,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4340,18 +4468,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -4370,7 +4498,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -4381,7 +4509,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -4400,25 +4528,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4430,25 +4558,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4460,18 +4588,18 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -4490,18 +4618,18 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -4520,25 +4648,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4550,25 +4678,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4580,25 +4708,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4610,25 +4738,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4640,25 +4768,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4670,18 +4798,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -4700,25 +4828,25 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4730,18 +4858,18 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -4760,7 +4888,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4771,14 +4899,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4790,25 +4918,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4820,25 +4948,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4850,18 +4978,18 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -4880,18 +5008,18 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -4910,18 +5038,18 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -4940,25 +5068,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4970,25 +5098,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5000,25 +5128,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5030,25 +5158,25 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5060,25 +5188,25 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5218,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -5101,14 +5229,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5120,25 +5248,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5150,25 +5278,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5308,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -5191,14 +5319,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5210,25 +5338,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5240,25 +5368,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5270,18 +5398,18 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -5300,25 +5428,25 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5330,25 +5458,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5360,18 +5488,18 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -5390,16 +5518,20 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
@@ -5416,25 +5548,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5578,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -5457,14 +5589,14 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5608,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -5487,7 +5619,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -5506,18 +5638,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -5536,7 +5668,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5566,18 +5698,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -5596,18 +5728,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -5626,25 +5758,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5656,18 +5788,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -5686,18 +5818,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -5716,18 +5848,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -5746,7 +5878,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -5776,7 +5908,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -5806,7 +5938,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -5824,7 +5956,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5968,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -5866,25 +5998,25 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5896,18 +6028,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -5926,25 +6058,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5956,18 +6088,18 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -5986,7 +6118,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>kyc31604</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -5997,7 +6129,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -6011,23 +6143,23 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -6041,12 +6173,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -6057,7 +6189,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -6071,12 +6203,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>non_buyer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kyc31604</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -6094,7 +6226,7 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6244,7 @@
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6136,18 +6268,18 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -6166,18 +6298,18 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -6196,18 +6328,18 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -6226,7 +6358,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -6256,18 +6388,18 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -6286,7 +6418,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -6316,18 +6448,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -6346,18 +6478,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -6376,18 +6508,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -6406,18 +6538,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -6436,18 +6568,18 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -6466,7 +6598,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -6477,7 +6609,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -6496,18 +6628,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -6526,18 +6658,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -6556,18 +6688,18 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -6586,7 +6718,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -6597,7 +6729,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -6616,18 +6748,18 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -6646,16 +6778,20 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
@@ -6672,16 +6808,20 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
@@ -6698,16 +6838,20 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
@@ -6724,18 +6868,18 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -6754,7 +6898,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -6765,7 +6909,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -6784,18 +6928,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -6814,18 +6958,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -6844,18 +6988,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -6874,18 +7018,18 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -6904,18 +7048,18 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -6934,18 +7078,18 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -6964,18 +7108,18 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -6994,18 +7138,18 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -7024,18 +7168,18 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -7054,18 +7198,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -7084,18 +7228,18 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -7114,18 +7258,18 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -7144,16 +7288,20 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
@@ -7170,7 +7318,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -7181,7 +7329,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -7200,16 +7348,20 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
@@ -7226,16 +7378,20 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
@@ -7252,7 +7408,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -7263,7 +7419,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -7282,18 +7438,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -7312,7 +7468,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -7323,7 +7479,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -7342,7 +7498,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -7353,7 +7509,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -7372,18 +7528,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -7402,7 +7558,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -7413,7 +7569,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -7432,18 +7588,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -7462,18 +7618,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -7492,13 +7648,13 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -7522,18 +7678,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -7552,7 +7708,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -7563,7 +7719,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -7577,30 +7733,30 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>cart_abandon</t>
+          <t>high_intent</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7612,18 +7768,18 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -7642,7 +7798,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -7653,14 +7809,14 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7672,18 +7828,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -7702,21 +7858,25 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7728,18 +7888,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -7758,25 +7918,25 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7788,25 +7948,25 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7818,13 +7978,13 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7848,7 +8008,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -7878,25 +8038,25 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7908,21 +8068,25 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7934,25 +8098,25 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -7964,7 +8128,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>kk_4832269209</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7975,14 +8139,14 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -7994,7 +8158,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -8005,14 +8169,14 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8024,18 +8188,18 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -8054,7 +8218,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -8065,14 +8229,14 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8248,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -8095,14 +8259,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8114,25 +8278,25 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8144,21 +8308,25 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr"/>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8170,18 +8338,18 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -8200,18 +8368,18 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -8230,18 +8398,18 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -8260,18 +8428,18 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -8290,18 +8458,18 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -8320,25 +8488,25 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8350,25 +8518,25 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8380,18 +8548,18 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -8410,7 +8578,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -8421,7 +8589,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -8440,18 +8608,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -8470,25 +8638,25 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8500,25 +8668,25 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8698,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -8560,13 +8728,13 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -8578,7 +8746,7 @@
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8590,25 +8758,25 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8788,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -8638,7 +8806,7 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8650,21 +8818,25 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8676,16 +8848,20 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
@@ -8702,16 +8878,20 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
@@ -8728,21 +8908,25 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8754,25 +8938,25 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8784,18 +8968,18 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -8814,25 +8998,25 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8844,18 +9028,18 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -8874,7 +9058,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -8885,7 +9069,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -8904,18 +9088,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -8934,7 +9118,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -8945,14 +9129,14 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9148,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -8975,14 +9159,14 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8994,25 +9178,25 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9024,13 +9208,13 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9054,7 +9238,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -9084,13 +9268,13 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9114,18 +9298,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -9144,25 +9328,25 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9174,25 +9358,25 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9204,18 +9388,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -9234,18 +9418,18 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -9264,25 +9448,25 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9294,18 +9478,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -9324,18 +9508,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -9354,25 +9538,25 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9384,25 +9568,25 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9414,18 +9598,18 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -9444,7 +9628,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -9455,7 +9639,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -9474,25 +9658,25 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9504,18 +9688,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -9534,21 +9718,25 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9560,18 +9748,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -9590,21 +9778,25 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9616,18 +9808,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -9646,21 +9838,25 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9672,21 +9868,25 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9898,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -9709,14 +9909,14 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9728,18 +9928,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -9758,13 +9958,13 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -9788,7 +9988,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -9799,7 +9999,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -9818,18 +10018,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F320" t="inlineStr"/>
@@ -9848,25 +10048,25 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9878,7 +10078,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -9889,7 +10089,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -9908,18 +10108,18 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -9938,18 +10138,18 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -9968,7 +10168,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -9979,14 +10179,14 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9998,18 +10198,18 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -10028,25 +10228,25 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10058,18 +10258,18 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -10088,18 +10288,18 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -10118,18 +10318,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -10148,13 +10348,13 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -10178,7 +10378,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -10196,7 +10396,7 @@
       <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10208,18 +10408,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -10227,186 +10427,6 @@
       <c r="H333" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>kk_4828870663</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>kk_4828729325</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>EFW</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>kk_4828995176</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>Heritage</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>kk_4828903098</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>HIGH_INTENT_NUDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>high_intent</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>kk_4828987324</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>naversa_mo</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>repeat_buyer</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>kk_4828788256</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>naver_brandsearch_mobile</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -3106,7 +3106,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -3466,7 +3466,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -4006,7 +4006,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -4816,7 +4816,7 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -4846,7 +4846,7 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4906,7 +4906,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -4936,7 +4936,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -5056,7 +5056,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -5206,7 +5206,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -8296,7 +8296,7 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -8416,7 +8416,7 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>kk_4833733292</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -8656,7 +8656,7 @@
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -8746,7 +8746,7 @@
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>kk_4832804456</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9238,13 +9238,13 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9256,7 +9256,7 @@
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9268,13 +9268,13 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9286,7 +9286,7 @@
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -9346,7 +9346,7 @@
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -9706,7 +9706,7 @@
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -9736,7 +9736,7 @@
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -9766,7 +9766,7 @@
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -9946,7 +9946,7 @@
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -9976,7 +9976,7 @@
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -10006,7 +10006,7 @@
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -10126,7 +10126,7 @@
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -10156,7 +10156,7 @@
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -451,27 +451,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>welko33</t>
+          <t>sotank</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01052950560</t>
+          <t>01090171948</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Heather Canyon II Jacket</t>
+          <t>M's Three Rock Jacket</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9867,22 +9867,22 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_3259942163</t>
+          <t>kk_2826668268</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01020489332</t>
+          <t>01074843858</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E338" t="inlineStr"/>
@@ -9895,22 +9895,22 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_2826668268</t>
+          <t>kk_3259942163</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01074843858</t>
+          <t>01020489332</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
@@ -10427,12 +10427,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>kk_3440880252</t>
+          <t>kk_4611877390</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>01023828239</t>
+          <t>01034010575</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>demendgen</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -10455,12 +10455,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>kk_4611877390</t>
+          <t>kk_3440880252</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>01034010575</t>
+          <t>01023828239</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>demendgen</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -11071,22 +11071,22 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>kk_4742048286</t>
+          <t>kk_3777466040</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>01046424731</t>
+          <t>01088374115</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -11099,22 +11099,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>kk_3777466040</t>
+          <t>kk_4742048286</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>01088374115</t>
+          <t>01046424731</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11155,12 +11155,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11183,12 +11183,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -13899,12 +13899,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>kk_3181390163</t>
+          <t>k8017544</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>01081430435</t>
+          <t>01095772982</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E482" t="inlineStr"/>
@@ -13927,12 +13927,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>k8017544</t>
+          <t>kk_3181390163</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>01095772982</t>
+          <t>01081430435</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E483" t="inlineStr"/>
@@ -14011,12 +14011,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>shon5072</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>01095777956</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14039,12 +14039,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>shon5072</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01095777956</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14291,22 +14291,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>kk_4915210068</t>
+          <t>kk_4000929133</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>01054111693</t>
+          <t>01029354130</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E496" t="inlineStr"/>
@@ -14319,22 +14319,22 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>kk_4000929133</t>
+          <t>kk_4915210068</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>01029354130</t>
+          <t>01054111693</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -15971,22 +15971,22 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>kk_4850097780</t>
+          <t>kk_4895148787</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>01053956505</t>
+          <t>01084770957</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_상시(2565MF,비구매자14일)</t>
         </is>
       </c>
       <c r="E556" t="inlineStr"/>
@@ -15999,22 +15999,22 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>kk_4895148787</t>
+          <t>kk_4850097780</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>01084770957</t>
+          <t>01053956505</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자14일)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E557" t="inlineStr"/>
@@ -17539,22 +17539,22 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E612" t="inlineStr"/>
@@ -17567,12 +17567,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>tomsnt70</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01053037290</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E613" t="inlineStr"/>
@@ -17595,22 +17595,22 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>tomsnt70</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>01053037290</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E614" t="inlineStr"/>
@@ -17819,12 +17819,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>kk_4511623737</t>
+          <t>jaejun8476</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>01076154343</t>
+          <t>01038228152</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -17847,12 +17847,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>jaejun8476</t>
+          <t>kk_4511623737</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>01038228152</t>
+          <t>01076154343</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -17931,22 +17931,22 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>kk_4963837369</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>01090642357</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -17959,22 +17959,22 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_4963837369</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01090642357</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
@@ -18071,12 +18071,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>kk_4883722134</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>01043573603</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E631" t="inlineStr"/>
@@ -18127,12 +18127,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_4883722134</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01043573603</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18351,22 +18351,22 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>kk_4747397154</t>
+          <t>kk_4588287948</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>01052568046</t>
+          <t>01091651067</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E641" t="inlineStr"/>
@@ -18379,22 +18379,22 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>kk_4588287948</t>
+          <t>kk_4747397154</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>01091651067</t>
+          <t>01052568046</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E642" t="inlineStr"/>
@@ -19023,22 +19023,22 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>fejou</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01020052547</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E665" t="inlineStr"/>
@@ -19051,22 +19051,22 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>fejou</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>01020052547</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E666" t="inlineStr"/>
@@ -19275,22 +19275,22 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>silverjida</t>
+          <t>hunylee</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>01028180759</t>
+          <t>01086334375</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E674" t="inlineStr"/>
@@ -19303,22 +19303,22 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>hunylee</t>
+          <t>silverjida</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>01086334375</t>
+          <t>01028180759</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E675" t="inlineStr"/>
@@ -19695,12 +19695,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -19710,7 +19710,7 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E689" t="inlineStr"/>
@@ -19723,12 +19723,12 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E690" t="inlineStr"/>
@@ -19919,22 +19919,22 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>kk_4279462373</t>
+          <t>kk_3230193702</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>01074618668</t>
+          <t>01035207654</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_260626_summerhiking</t>
+          <t>[PF]전환_상시(2565MF,비구매자14일)</t>
         </is>
       </c>
       <c r="E697" t="inlineStr"/>
@@ -19975,22 +19975,22 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>kk_3230193702</t>
+          <t>kk_4279462373</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01035207654</t>
+          <t>01074618668</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자14일)</t>
+          <t>KAKAO_CH_MESSAGE_260626_summerhiking</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -20059,22 +20059,22 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>kk_4860725024</t>
+          <t>conpak</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>01042399655</t>
+          <t>01090742031</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E702" t="inlineStr"/>
@@ -20087,22 +20087,22 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>conpak</t>
+          <t>kk_4860725024</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>01090742031</t>
+          <t>01042399655</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
         </is>
       </c>
       <c r="E703" t="inlineStr"/>
@@ -20787,22 +20787,22 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E728" t="inlineStr"/>
@@ -20815,22 +20815,22 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E729" t="inlineStr"/>
@@ -21459,12 +21459,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
@@ -21487,12 +21487,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E753" t="inlineStr"/>
@@ -21655,12 +21655,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>kk_4614679325</t>
+          <t>leeyh015</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>01063402986</t>
+          <t>01020785413</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E759" t="inlineStr"/>
@@ -21683,12 +21683,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>leeyh015</t>
+          <t>kk_4614679325</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01020785413</t>
+          <t>01063402986</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
@@ -21767,22 +21767,22 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E763" t="inlineStr"/>
@@ -21795,22 +21795,22 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E764" t="inlineStr"/>
@@ -21851,12 +21851,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -21879,12 +21879,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -21935,12 +21935,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>kk_4688432632</t>
+          <t>kk_4645594639</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01081882909</t>
+          <t>01076731349</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -21950,7 +21950,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
@@ -21963,12 +21963,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>kk_4645594639</t>
+          <t>kk_4688432632</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>01076731349</t>
+          <t>01081882909</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E770" t="inlineStr"/>
@@ -22187,12 +22187,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>sims0328mis</t>
+          <t>youngv7</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>01087510925</t>
+          <t>01030111622</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E778" t="inlineStr"/>
@@ -22215,12 +22215,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>youngv7</t>
+          <t>sims0328mis</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01030111622</t>
+          <t>01087510925</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
       <c r="E779" t="inlineStr"/>
@@ -22383,12 +22383,12 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>kk_4864045300</t>
+          <t>kk_4376700680</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>01089985309</t>
+          <t>01047096832</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0425_FAMILYSALE</t>
         </is>
       </c>
       <c r="E785" t="inlineStr"/>
@@ -22411,12 +22411,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>kk_4376700680</t>
+          <t>kk_4864045300</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01047096832</t>
+          <t>01089985309</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0425_FAMILYSALE</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22467,22 +22467,22 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E788" t="inlineStr"/>
@@ -22495,22 +22495,22 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E789" t="inlineStr"/>
@@ -22971,22 +22971,22 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>cdoo1981</t>
+          <t>wocl12</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>01028113501</t>
+          <t>01075778014</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E806" t="inlineStr"/>
@@ -22999,22 +22999,22 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>wocl12</t>
+          <t>kk_3913739580</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>01075778014</t>
+          <t>01085451631</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E807" t="inlineStr"/>
@@ -23027,12 +23027,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>kk_3913739580</t>
+          <t>cdoo1981</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>01085451631</t>
+          <t>01028113501</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -23042,7 +23042,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E808" t="inlineStr"/>
@@ -23055,22 +23055,22 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>kk_3383329401</t>
+          <t>lutralutra</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>01032973213</t>
+          <t>01089828175</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E809" t="inlineStr"/>
@@ -23083,22 +23083,22 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>lutralutra</t>
+          <t>kk_3969429343</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>01089828175</t>
+          <t>01076896114</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E810" t="inlineStr"/>
@@ -23111,12 +23111,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>kk_3854796628</t>
+          <t>kk_3383329401</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>01051880876</t>
+          <t>01032973213</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E811" t="inlineStr"/>
@@ -23139,12 +23139,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>kk_3969429343</t>
+          <t>kk_3854796628</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>01076896114</t>
+          <t>01051880876</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E812" t="inlineStr"/>
@@ -23279,12 +23279,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>judges</t>
+          <t>kk_3693498386</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>01054486363</t>
+          <t>01043995752</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E817" t="inlineStr"/>
@@ -23307,12 +23307,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>kk_3693498386</t>
+          <t>judges</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>01043995752</t>
+          <t>01054486363</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -23322,7 +23322,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E818" t="inlineStr"/>
@@ -23475,12 +23475,12 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>ecarlt</t>
+          <t>goodf3</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>01089294239</t>
+          <t>01027046933</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -23503,12 +23503,12 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>mul6181</t>
+          <t>ecarlt</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>01025152363</t>
+          <t>01089294239</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E825" t="inlineStr"/>
@@ -23531,12 +23531,12 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>goodf3</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01027046933</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,12 +23559,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>mul6181</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01025152363</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,22 +23615,22 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>sun5861</t>
+          <t>kk_4353400508</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01094595790</t>
+          <t>01088603566</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,22 +23643,22 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4353400508</t>
+          <t>sun5861</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01088603566</t>
+          <t>01094595790</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -23727,22 +23727,22 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>kk_4855218048</t>
+          <t>kk_3180500266</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>01038521097</t>
+          <t>01054795099</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E833" t="inlineStr"/>
@@ -23755,22 +23755,22 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>kk_3180500266</t>
+          <t>kk_4855218048</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>01054795099</t>
+          <t>01038521097</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E834" t="inlineStr"/>
@@ -23839,12 +23839,12 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>kk_4774969197</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>01087827185</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E837" t="inlineStr"/>
@@ -23867,12 +23867,12 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_4774969197</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01087827185</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -23882,7 +23882,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E838" t="inlineStr"/>
@@ -23895,12 +23895,12 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>kk_3884439990</t>
+          <t>kk_3727986361</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>01071670041</t>
+          <t>01045693585</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E839" t="inlineStr"/>
@@ -23923,12 +23923,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>kk_3727986361</t>
+          <t>kk_3884439990</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>01045693585</t>
+          <t>01071670041</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -23938,7 +23938,7 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E840" t="inlineStr"/>
@@ -25911,22 +25911,22 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_3321938840</t>
+          <t>wjsgml107</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01042233082</t>
+          <t>01020483694</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E911" t="inlineStr"/>
@@ -25939,22 +25939,22 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>wjsgml107</t>
+          <t>kk_3321938840</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>01020483694</t>
+          <t>01042233082</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E912" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inhip</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01027705324</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -543,22 +543,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_2873136069</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01048866068</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -571,22 +571,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_3864149982</t>
+          <t>inhip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01025551942</t>
+          <t>01027705324</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -599,22 +599,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>kk_2873136069</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01048866068</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -627,22 +627,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cool2vs2</t>
+          <t>kk_3864149982</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01027216492</t>
+          <t>01025551942</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -655,22 +655,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4293495304</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01032960676</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -683,22 +683,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tjsgksrlf123</t>
+          <t>cool2vs2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01033775889</t>
+          <t>01027216492</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDM_0126_bestreview</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -711,22 +711,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4446330406</t>
+          <t>kk_4293495304</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01027816365</t>
+          <t>01032960676</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -739,12 +739,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>magazz</t>
+          <t>tjsgksrlf123</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01099409643</t>
+          <t>01033775889</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0126_bestreview</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -767,22 +767,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>kk_4446330406</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01027816365</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -795,12 +795,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>speedking</t>
+          <t>magazz</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01051344025</t>
+          <t>01099409643</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -823,22 +823,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jhoh55555</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01062626688</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -851,22 +851,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hennessy</t>
+          <t>speedking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01030027773</t>
+          <t>01051344025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -879,22 +879,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_3803973742</t>
+          <t>jhoh55555</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01062581642</t>
+          <t>01062626688</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -907,22 +907,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>psw242</t>
+          <t>hennessy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01054125832</t>
+          <t>01030027773</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -935,22 +935,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>kk_3803973742</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062581642</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -963,22 +963,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4793170858</t>
+          <t>psw242</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01077026417</t>
+          <t>01054125832</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -991,22 +991,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1019,22 +1019,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>arrtieom</t>
+          <t>kk_4793170858</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01071593949</t>
+          <t>01077026417</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1047,12 +1047,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4778273271</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01029527548</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eastrain9</t>
+          <t>arrtieom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01071445034</t>
+          <t>01071593949</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1103,12 +1103,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>kk_4778273271</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01029527548</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1131,22 +1131,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gidongi</t>
+          <t>eastrain9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01064373200</t>
+          <t>01071445034</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1159,12 +1159,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4323824634</t>
+          <t>greom73</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01021939477</t>
+          <t>01086372526</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1187,22 +1187,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>gidongi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01064373200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1215,12 +1215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chan680</t>
+          <t>kk_4323824634</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01026244284</t>
+          <t>01021939477</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1243,22 +1243,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4276234081</t>
+          <t>skku2738</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01046630168</t>
+          <t>01074152738</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1271,22 +1271,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jhyeon41</t>
+          <t>chan680</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01038106019</t>
+          <t>01026244284</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1299,12 +1299,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_2826785228</t>
+          <t>kk_4276234081</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01022372658</t>
+          <t>01046630168</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1327,22 +1327,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_3511421009</t>
+          <t>jhyeon41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01031496540</t>
+          <t>01038106019</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1355,12 +1355,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4806290091</t>
+          <t>kk_2826785228</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01042848444</t>
+          <t>01022372658</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1383,22 +1383,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>serica22</t>
+          <t>kk_3511421009</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01095513653</t>
+          <t>01031496540</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0705_SEASON_OFF_2ND</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1411,22 +1411,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_4806290091</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01042848444</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1439,22 +1439,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>serica22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01095513653</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0705_SEASON_OFF_2ND</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1467,22 +1467,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ysc1111</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01041763874</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1495,12 +1495,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1523,12 +1523,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3097873244</t>
+          <t>ysc1111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01032060915</t>
+          <t>01041763874</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1551,12 +1551,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>alonzo22</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01062838804</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1579,22 +1579,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3746984520</t>
+          <t>kk_3097873244</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01029951804</t>
+          <t>01032060915</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1607,12 +1607,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3895206189</t>
+          <t>alonzo22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01043980107</t>
+          <t>01062838804</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1635,22 +1635,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>k8017544</t>
+          <t>kk_3746984520</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01095772982</t>
+          <t>01029951804</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1663,22 +1663,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4745169563</t>
+          <t>kk_3895206189</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01047026526</t>
+          <t>01043980107</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1691,22 +1691,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>djak0712</t>
+          <t>k8017544</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01063559841</t>
+          <t>01095772982</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1719,22 +1719,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gunnie234</t>
+          <t>kk_4745169563</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01099652641</t>
+          <t>01047026526</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1747,17 +1747,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4946126994</t>
+          <t>djak0712</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01055149084</t>
+          <t>01063559841</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1775,22 +1775,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>gunnie234</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01099652641</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1803,12 +1803,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>oshibun</t>
+          <t>kk_4946126994</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01029500259</t>
+          <t>01055149084</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1831,22 +1831,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3042011585</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01073685152</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1859,22 +1859,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>oshibun</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01029500259</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1887,12 +1887,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_3042011585</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01073685152</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1915,22 +1915,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>passion1984</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01064630333</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1943,17 +1943,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4656100370</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01091056580</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1971,12 +1971,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1999,12 +1999,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>redblood271</t>
+          <t>kk_4656100370</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01031572135</t>
+          <t>01091056580</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2027,12 +2027,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2055,22 +2055,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3224620899</t>
+          <t>redblood271</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01085627400</t>
+          <t>01031572135</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2083,22 +2083,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kkhgreen</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01092780969</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2111,12 +2111,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4319428238</t>
+          <t>kk_3224620899</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01092785785</t>
+          <t>01085627400</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2139,12 +2139,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3941500642</t>
+          <t>kkhgreen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01074450002</t>
+          <t>01092780969</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2167,12 +2167,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>beki76</t>
+          <t>kk_4319428238</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01088004778</t>
+          <t>01092785785</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2195,22 +2195,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pck490210</t>
+          <t>kk_3941500642</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01025491031</t>
+          <t>01074450002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2223,22 +2223,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>matmata</t>
+          <t>beki76</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01084207951</t>
+          <t>01088004778</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2251,12 +2251,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3977151705</t>
+          <t>pck490210</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01025952746</t>
+          <t>01025491031</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2279,12 +2279,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>terran1123</t>
+          <t>matmata</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01053324395</t>
+          <t>01084207951</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2307,22 +2307,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3977151705</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01025952746</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2335,22 +2335,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bbijim</t>
+          <t>terran1123</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01086676776</t>
+          <t>01053324395</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2363,12 +2363,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3297492631</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01022470507</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2391,22 +2391,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rudalsla</t>
+          <t>bbijim</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01071949782</t>
+          <t>01086676776</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2419,12 +2419,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cubewheel</t>
+          <t>kk_3297492631</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01089546320</t>
+          <t>01022470507</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2447,22 +2447,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>rudalsla</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01071949782</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2475,12 +2475,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4991395508</t>
+          <t>cubewheel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01025638959</t>
+          <t>01089546320</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2503,22 +2503,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_2988538598</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01055855280</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2531,22 +2531,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3180798849</t>
+          <t>kk_4991395508</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01086259207</t>
+          <t>01025638959</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2559,22 +2559,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3949933982</t>
+          <t>kk_2988538598</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01026968241</t>
+          <t>01055855280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gitae76</t>
+          <t>kk_3180798849</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01020801107</t>
+          <t>01086259207</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2615,12 +2615,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3182573827</t>
+          <t>kk_3949933982</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01077419077</t>
+          <t>01026968241</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2643,12 +2643,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>gitae76</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01020801107</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2671,22 +2671,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>prologic</t>
+          <t>kk_3182573827</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01090864344</t>
+          <t>01077419077</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4863256269</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01027382913</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2727,12 +2727,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>insangpa72</t>
+          <t>prologic</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01053035171</t>
+          <t>01090864344</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2755,12 +2755,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bjh4895</t>
+          <t>kk_4863256269</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01042374895</t>
+          <t>01027382913</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2783,22 +2783,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kjjopen</t>
+          <t>insangpa72</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01086035744</t>
+          <t>01053035171</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2811,22 +2811,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3425319183</t>
+          <t>bjh4895</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01073728534</t>
+          <t>01042374895</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2839,22 +2839,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>blackout9</t>
+          <t>kjjopen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01054444345</t>
+          <t>01086035744</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2867,12 +2867,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_3425319183</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01073728534</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2895,22 +2895,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3522301091</t>
+          <t>blackout9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01088731863</t>
+          <t>01054444345</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2923,12 +2923,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2951,12 +2951,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>garfield98</t>
+          <t>kk_3522301091</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01032643963</t>
+          <t>01088731863</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2979,12 +2979,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3007,12 +3007,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4355884570</t>
+          <t>garfield98</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01052096279</t>
+          <t>01032643963</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3035,22 +3035,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4785141094</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01022106967</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3063,22 +3063,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>king1090</t>
+          <t>kk_4355884570</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01064003306</t>
+          <t>01052096279</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mo21613</t>
+          <t>kk_4785141094</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01063041255</t>
+          <t>01022106967</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3119,22 +3119,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>johun0414</t>
+          <t>king1090</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01082150607</t>
+          <t>01064003306</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3147,17 +3147,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4313489248</t>
+          <t>mo21613</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01026591380</t>
+          <t>01063041255</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3175,22 +3175,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_3781116310</t>
+          <t>johun0414</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01052721277</t>
+          <t>01082150607</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3203,12 +3203,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>gun9670</t>
+          <t>kk_4313489248</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01051514803</t>
+          <t>01026591380</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3231,22 +3231,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3781116310</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01052721277</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3259,12 +3259,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3941904586</t>
+          <t>gun9670</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01067078239</t>
+          <t>01051514803</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3287,12 +3287,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3315,12 +3315,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3478853991</t>
+          <t>kk_3941904586</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01077662474</t>
+          <t>01067078239</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3343,12 +3343,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3738826876</t>
+          <t>kk_4993751323</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01095514239</t>
+          <t>01053138487</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3371,12 +3371,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>hg1890</t>
+          <t>kk_3478853991</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01038436423</t>
+          <t>01077662474</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3399,12 +3399,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>hiwoong76</t>
+          <t>kk_3738826876</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01067981478</t>
+          <t>01095514239</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3427,12 +3427,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3225675516</t>
+          <t>hg1890</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01022881015</t>
+          <t>01038436423</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EDM_0226</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nbhfrancisco</t>
+          <t>hiwoong76</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01050977100</t>
+          <t>01067981478</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3483,12 +3483,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4678957107</t>
+          <t>kk_3225675516</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01034388709</t>
+          <t>01022881015</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>EDM_0226</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3511,22 +3511,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>jung03</t>
+          <t>nbhfrancisco</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01026209151</t>
+          <t>01050977100</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3539,22 +3539,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>yoichi</t>
+          <t>kk_4678957107</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01072692907</t>
+          <t>01034388709</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3567,22 +3567,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3933214484</t>
+          <t>jung03</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01090832304</t>
+          <t>01026209151</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3595,12 +3595,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4940441538</t>
+          <t>yoichi</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01089269967</t>
+          <t>01072692907</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3623,12 +3623,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3933214484</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01090832304</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3651,22 +3651,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3240277946</t>
+          <t>kk_4940441538</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01049229190</t>
+          <t>01089269967</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3679,12 +3679,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4727133236</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01064755009</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3707,22 +3707,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>nayuna1022</t>
+          <t>kk_3240277946</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01062175214</t>
+          <t>01049229190</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3735,12 +3735,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>kk_4727133236</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01064755009</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3763,22 +3763,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>nayuna1022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01062175214</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3791,22 +3791,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>yjookim67</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01054114855</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3819,22 +3819,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>camha</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01031331918</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3847,22 +3847,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dawonint</t>
+          <t>yjookim67</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01037690185</t>
+          <t>01054114855</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -3875,12 +3875,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>camha</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01031331918</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3903,22 +3903,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>dawonint</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01037690185</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3931,22 +3931,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jswoo99</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01031705383</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3959,22 +3959,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3179544090</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01095352220</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3987,22 +3987,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4796376423</t>
+          <t>jswoo99</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01035771357</t>
+          <t>01031705383</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4015,22 +4015,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3363127172</t>
+          <t>kk_3179544090</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01072739372</t>
+          <t>01095352220</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4043,12 +4043,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4804817546</t>
+          <t>kk_4796376423</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01048111806</t>
+          <t>01035771357</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4071,22 +4071,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4929674815</t>
+          <t>kk_3363127172</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01075264562</t>
+          <t>01072739372</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4099,22 +4099,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>his9742</t>
+          <t>kk_4804817546</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01024949742</t>
+          <t>01048111806</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4127,22 +4127,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ils1706</t>
+          <t>kk_4929674815</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01037004519</t>
+          <t>01075264562</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4155,22 +4155,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_3477586140</t>
+          <t>his9742</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01066698868</t>
+          <t>01024949742</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4183,12 +4183,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jklee1316</t>
+          <t>ils1706</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01023358588</t>
+          <t>01037004519</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4211,22 +4211,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3778944759</t>
+          <t>kk_3477586140</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01066975193</t>
+          <t>01066698868</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4239,22 +4239,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ino326</t>
+          <t>jklee1316</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01024921837</t>
+          <t>01023358588</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4267,12 +4267,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4378858812_2</t>
+          <t>kk_3778944759</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01090939890</t>
+          <t>01066975193</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4295,22 +4295,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4300806197</t>
+          <t>ino326</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01045551631</t>
+          <t>01024921837</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4323,12 +4323,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4880545805</t>
+          <t>kk_4378858812_2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01022237436</t>
+          <t>01090939890</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>by5500</t>
+          <t>kk_4300806197</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01071770101</t>
+          <t>01045551631</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4379,12 +4379,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3246810283</t>
+          <t>kk_4880545805</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01039315369</t>
+          <t>01022237436</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4407,22 +4407,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>show5430</t>
+          <t>by5500</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01099500131</t>
+          <t>01071770101</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4435,22 +4435,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>xcable</t>
+          <t>kk_3246810283</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01080043359</t>
+          <t>01039315369</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4463,12 +4463,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>lsu3080</t>
+          <t>show5430</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01068283080</t>
+          <t>01099500131</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4491,22 +4491,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_2762161146</t>
+          <t>xcable</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01046533615</t>
+          <t>01080043359</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LMS_ECOM_GnR</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4519,22 +4519,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_3212536253</t>
+          <t>lsu3080</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01097992453</t>
+          <t>01068283080</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4547,12 +4547,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_2762161146</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01046533615</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_GnR</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4575,12 +4575,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>policejs</t>
+          <t>kk_3212536253</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01041704743</t>
+          <t>01097992453</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4603,12 +4603,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4631,22 +4631,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>policejs</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01041704743</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4659,22 +4659,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>yksik0528</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01033992431</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4687,22 +4687,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4693581167</t>
+          <t>hajd1011</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01050127862</t>
+          <t>01054401373</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4715,22 +4715,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4881694655</t>
+          <t>yksik0528</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01072580898</t>
+          <t>01033992431</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4743,22 +4743,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4702753709</t>
+          <t>kk_4693581167</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01076663512</t>
+          <t>01050127862</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4771,12 +4771,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>net1122</t>
+          <t>kk_4881694655</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01040964937</t>
+          <t>01072580898</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4799,12 +4799,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4927707365</t>
+          <t>kk_4702753709</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01053829303</t>
+          <t>01076663512</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4827,12 +4827,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>koreankim</t>
+          <t>net1122</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01095372588</t>
+          <t>01040964937</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4855,12 +4855,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3181446328</t>
+          <t>kk_4927707365</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01086441161</t>
+          <t>01053829303</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4883,12 +4883,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>koreankim</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01095372588</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4911,12 +4911,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4360429720</t>
+          <t>kk_3181446328</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01089099036</t>
+          <t>01086441161</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4939,12 +4939,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4967,12 +4967,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4703845503</t>
+          <t>kk_4360429720</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01057372401</t>
+          <t>01089099036</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4995,12 +4995,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_3763845552</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01095701533</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5023,22 +5023,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>luvieye123</t>
+          <t>kk_4703845503</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01035949045</t>
+          <t>01057372401</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5051,22 +5051,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>pooo1228</t>
+          <t>kk_3763845552</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01062724056</t>
+          <t>01095701533</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5079,22 +5079,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_3380720822</t>
+          <t>luvieye123</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01054705220</t>
+          <t>01035949045</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5107,12 +5107,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3305072060</t>
+          <t>pooo1228</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01085390140</t>
+          <t>01062724056</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,논타겟)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5135,12 +5135,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4409064497</t>
+          <t>kk_3380720822</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01057371727</t>
+          <t>01054705220</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -5163,12 +5163,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4430409947</t>
+          <t>kk_3305072060</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01047358234</t>
+          <t>01085390140</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -5191,22 +5191,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>lefy</t>
+          <t>kk_4409064497</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01022414020</t>
+          <t>01057371727</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5219,22 +5219,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>varkala1</t>
+          <t>kk_4430409947</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01080276669</t>
+          <t>01047358234</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5247,22 +5247,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>njp0710</t>
+          <t>lefy</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01027282087</t>
+          <t>01022414020</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0610</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5275,12 +5275,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>varkala1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01080276669</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>cshc</t>
+          <t>njp0710</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01053437643</t>
+          <t>01027282087</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>0610</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5331,22 +5331,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>thebebob</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01094365308</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5359,12 +5359,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>cshc</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01053437643</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5387,22 +5387,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>thebebob</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01094365308</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5443,12 +5443,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>zxcvziii</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01048169121</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5471,12 +5471,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5499,12 +5499,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>zxcvziii</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01048169121</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5527,22 +5527,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4461497985</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01063241461</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5555,12 +5555,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4739241016</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01082593038</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5583,22 +5583,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4461497985</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01063241461</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5611,22 +5611,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ckddus2</t>
+          <t>kk_4739241016</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01048722142</t>
+          <t>01082593038</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MOhomelink</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5639,12 +5639,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>juks2761</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01062646133</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0129</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5667,12 +5667,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4659940912</t>
+          <t>ckddus2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01041612810</t>
+          <t>01048722142</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>MOhomelink</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5695,12 +5695,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>jyjangcti</t>
+          <t>juks2761</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01029378908</t>
+          <t>01062646133</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>LMS_ECOM_0129</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5723,22 +5723,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rao2001</t>
+          <t>kk_4659940912</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01025653293</t>
+          <t>01041612810</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5751,22 +5751,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jyjangcti</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01063315178</t>
+          <t>01029378908</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5779,12 +5779,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>bong9ya</t>
+          <t>rao2001</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01045637364</t>
+          <t>01025653293</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5807,12 +5807,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>lcs3017</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01094123017</t>
+          <t>01063315178</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5835,12 +5835,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ljw855</t>
+          <t>bong9ya</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01041724332</t>
+          <t>01045637364</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -5863,22 +5863,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>amistrong</t>
+          <t>lcs3017</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01055097870</t>
+          <t>01094123017</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5891,22 +5891,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>boxyogo</t>
+          <t>ljw855</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01047175275</t>
+          <t>01041724332</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5919,22 +5919,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4711669963</t>
+          <t>amistrong</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01053480904</t>
+          <t>01055097870</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5947,22 +5947,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3626975387</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01088796035</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5975,22 +5975,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_3100841256</t>
+          <t>kk_4711669963</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01054473961</t>
+          <t>01053480904</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -6003,12 +6003,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4339204533</t>
+          <t>kk_3626975387</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01064869716</t>
+          <t>01088796035</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -6031,12 +6031,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4826700021</t>
+          <t>kk_3100841256</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01066078107</t>
+          <t>01054473961</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -6059,12 +6059,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4240554258</t>
+          <t>kk_4339204533</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01035989843</t>
+          <t>01064869716</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6087,22 +6087,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826700021</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01066078107</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6115,22 +6115,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_4240554258</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01035989843</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6143,12 +6143,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>dimejin</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01086058650</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -6171,12 +6171,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kjh30201236</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01030204946</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6199,12 +6199,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_2847176143</t>
+          <t>dimejin</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01038261331</t>
+          <t>01086058650</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6227,12 +6227,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_3170960220</t>
+          <t>kjh30201236</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01087729278</t>
+          <t>01030204946</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6255,22 +6255,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4748122429</t>
+          <t>kk_2847176143</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01089229240</t>
+          <t>01038261331</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6283,22 +6283,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4545437798</t>
+          <t>kk_3170960220</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01021996968</t>
+          <t>01087729278</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -6311,22 +6311,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_3728489315</t>
+          <t>kk_4748122429</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01088859514</t>
+          <t>01089229240</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6339,22 +6339,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>nexen1974a</t>
+          <t>kk_4545437798</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01055782215</t>
+          <t>01021996968</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6367,22 +6367,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4648812045</t>
+          <t>kk_3728489315</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01045190963</t>
+          <t>01088859514</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -6395,17 +6395,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3621695729</t>
+          <t>nexen1974a</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01053495037</t>
+          <t>01055782215</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6423,12 +6423,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_4789987921</t>
+          <t>kk_4648812045</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01053009139</t>
+          <t>01045190963</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6451,12 +6451,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>lov2jjin</t>
+          <t>kk_3621695729</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01087038707</t>
+          <t>01053495037</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6479,12 +6479,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>jakelee</t>
+          <t>kk_4789987921</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01027223531</t>
+          <t>01053009139</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6507,12 +6507,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4391641739</t>
+          <t>lov2jjin</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01091994491</t>
+          <t>01087038707</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_2873620176</t>
+          <t>jakelee</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01029480082</t>
+          <t>01027223531</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6563,12 +6563,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4660550146</t>
+          <t>kk_4391641739</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01022238698</t>
+          <t>01091994491</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -6591,22 +6591,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kji5472</t>
+          <t>kk_2873620176</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01022054672</t>
+          <t>01029480082</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -6619,12 +6619,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4660550146</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01022238698</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6647,12 +6647,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_3260158755</t>
+          <t>kji5472</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01038984931</t>
+          <t>01022054672</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6675,12 +6675,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>shon5072</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01095777956</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -6703,22 +6703,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>mijlove</t>
+          <t>kk_3260158755</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01092285002</t>
+          <t>01038984931</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -6731,22 +6731,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>nicole</t>
+          <t>shon5072</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01083410822</t>
+          <t>01095777956</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -6759,22 +6759,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>yahoo0402</t>
+          <t>mijlove</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01050319361</t>
+          <t>01092285002</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -6787,22 +6787,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4848752733</t>
+          <t>nicole</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01090534422</t>
+          <t>01083410822</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -6815,22 +6815,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_4825328334</t>
+          <t>yahoo0402</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01022625558</t>
+          <t>01050319361</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -6843,12 +6843,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_4711817746</t>
+          <t>kk_4848752733</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01073740979</t>
+          <t>01090534422</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -6871,22 +6871,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3914085758</t>
+          <t>kk_4825328334</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01031872338</t>
+          <t>01022625558</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -6899,12 +6899,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4896487866</t>
+          <t>kk_4711817746</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01050400311</t>
+          <t>01073740979</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -6927,12 +6927,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3227570959</t>
+          <t>kk_3914085758</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01028169084</t>
+          <t>01031872338</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>segyung2</t>
+          <t>kk_4896487866</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01089808520</t>
+          <t>01050400311</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -6983,22 +6983,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>kk_3227570959</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01028169084</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7011,12 +7011,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>segyung2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01089808520</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7039,12 +7039,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_3607933321</t>
+          <t>sclpion</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01035122820</t>
+          <t>01088740653</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7067,22 +7067,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4481949959</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01077434037</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7095,12 +7095,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4860720956</t>
+          <t>kk_3607933321</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01056709617</t>
+          <t>01035122820</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7123,12 +7123,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4467979962</t>
+          <t>kk_4481949959</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01037751563</t>
+          <t>01077434037</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7151,12 +7151,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_2770056564</t>
+          <t>kk_4860720956</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01097609451</t>
+          <t>01056709617</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7179,12 +7179,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_5009517640</t>
+          <t>kk_4467979962</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01090817520</t>
+          <t>01037751563</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7207,22 +7207,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ryeol1004</t>
+          <t>kk_5009517640</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01087308928</t>
+          <t>01090817520</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7235,12 +7235,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>chk1987</t>
+          <t>kk_2770056564</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01067608088</t>
+          <t>01097609451</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7263,22 +7263,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_4520208596</t>
+          <t>ryeol1004</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01025741462</t>
+          <t>01087308928</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -7291,22 +7291,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3182043466</t>
+          <t>chk1987</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01092562936</t>
+          <t>01067608088</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7319,22 +7319,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4520208596</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01025741462</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -7347,22 +7347,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>pearl52</t>
+          <t>kk_3182043466</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01050351018</t>
+          <t>01092562936</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -7375,22 +7375,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kk_4929043811</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01037904341</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -7403,12 +7403,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4673119425</t>
+          <t>pearl52</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01085632266</t>
+          <t>01050351018</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_3639045388</t>
+          <t>kk_4929043811</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01064334743</t>
+          <t>01037904341</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -7459,12 +7459,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>kk_4673119425</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01085632266</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naversa_pc</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -7487,22 +7487,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4744667185</t>
+          <t>kk_3639045388</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01047226521</t>
+          <t>01064334743</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -7515,22 +7515,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4744667185</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01047226521</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -7543,22 +7543,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_3337408762</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01095768922</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -7571,22 +7571,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4650374928</t>
+          <t>kk_3337408762</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01086157107</t>
+          <t>01095768922</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -7599,22 +7599,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_3388290079</t>
+          <t>kk_4650374928</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01083191557</t>
+          <t>01086157107</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>kakao_ch_message_0325_s26new_cta</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -7627,12 +7627,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ysj1127</t>
+          <t>kk_3388290079</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01071109388</t>
+          <t>01083191557</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>kakao_ch_message_0325_s26new_cta</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -7655,12 +7655,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>pyhlove53</t>
+          <t>ysj1127</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01094031004</t>
+          <t>01071109388</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -7683,22 +7683,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>pyhlove53</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01094031004</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -7711,12 +7711,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ddolme</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01050040644</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -7739,22 +7739,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4416125651</t>
+          <t>ddolme</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01052177552</t>
+          <t>01050040644</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -7767,22 +7767,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>bbjj2000</t>
+          <t>kk_4416125651</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01035218300</t>
+          <t>01052177552</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -7795,22 +7795,22 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>sih92</t>
+          <t>bbjj2000</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01029623377</t>
+          <t>01035218300</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -7823,22 +7823,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_3835565251</t>
+          <t>sih92</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01027409786</t>
+          <t>01029623377</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -7851,12 +7851,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kingjo</t>
+          <t>kk_3835565251</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01062660099</t>
+          <t>01027409786</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -7879,12 +7879,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>guswo7310</t>
+          <t>kingjo</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01044712040</t>
+          <t>01062660099</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -7907,22 +7907,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_2807327385</t>
+          <t>guswo7310</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01038584194</t>
+          <t>01044712040</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -7935,22 +7935,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_3639576029</t>
+          <t>kk_2807327385</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01063967727</t>
+          <t>01038584194</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -7963,22 +7963,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4936216487</t>
+          <t>kk_3639576029</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01045751707</t>
+          <t>01063967727</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>pivy87</t>
+          <t>kk_4936216487</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01063819999</t>
+          <t>01045751707</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -8019,12 +8019,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_2826668268</t>
+          <t>pivy87</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01074843858</t>
+          <t>01063819999</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -8047,17 +8047,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>joontak</t>
+          <t>kk_2826668268</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01088917848</t>
+          <t>01074843858</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8075,22 +8075,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_4635961106</t>
+          <t>joontak</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01027884773</t>
+          <t>01088917848</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -8103,22 +8103,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_3949518630</t>
+          <t>kk_4635961106</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01033587883</t>
+          <t>01027884773</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -8131,12 +8131,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>hyundoart</t>
+          <t>kk_3949518630</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01096853214</t>
+          <t>01033587883</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -8159,12 +8159,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4600202212</t>
+          <t>hyundoart</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01095679374</t>
+          <t>01096853214</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -8187,22 +8187,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4503210270</t>
+          <t>kk_4600202212</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01071098993</t>
+          <t>01095679374</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -8215,12 +8215,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>kk_4503210270</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01071098993</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -8243,12 +8243,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_4750629166</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01065748515</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -8271,22 +8271,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4746271433</t>
+          <t>kk_4750629166</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01088977839</t>
+          <t>01065748515</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -8299,12 +8299,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>mondora</t>
+          <t>kk_4746271433</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01026379832</t>
+          <t>01088977839</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>EDM_0305</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8327,22 +8327,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>mondora</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01026379832</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0305</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -8355,22 +8355,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_4869187470</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01064823221</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -8383,22 +8383,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_3722415174</t>
+          <t>kk_4869187470</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01036589994</t>
+          <t>01064823221</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8411,12 +8411,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>loxolist</t>
+          <t>kk_3722415174</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01068552419</t>
+          <t>01036589994</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8439,22 +8439,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>oh8314</t>
+          <t>loxolist</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01090595921</t>
+          <t>01068552419</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>lf</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -8467,22 +8467,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_3825664300</t>
+          <t>oh8314</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01040323452</t>
+          <t>01090595921</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>lf</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -8495,22 +8495,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ustar777</t>
+          <t>kk_3825664300</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01027424281</t>
+          <t>01040323452</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -8523,22 +8523,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>cjonghak</t>
+          <t>ustar777</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01090444081</t>
+          <t>01027424281</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8551,22 +8551,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>cjonghak</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01090444081</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8579,12 +8579,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -11603,22 +11603,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>jaeho86</t>
+          <t>aurora1530</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01091199057</t>
+          <t>01090756922</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11631,22 +11631,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>aurora1530</t>
+          <t>jaeho86</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01090756922</t>
+          <t>01091199057</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -12751,22 +12751,22 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>kk_3181390163</t>
+          <t>kk_4486967764</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>01081430435</t>
+          <t>01095303556</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -12779,22 +12779,22 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>kk_4486967764</t>
+          <t>kk_3181390163</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>01095303556</t>
+          <t>01081430435</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -13087,12 +13087,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -13115,12 +13115,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -13507,12 +13507,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13535,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -14319,12 +14319,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>kk_3846090083</t>
+          <t>kk_4850097780</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>01062091126</t>
+          <t>01053956505</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -14347,12 +14347,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>kk_4850097780</t>
+          <t>kk_3846090083</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>01053956505</t>
+          <t>01062091126</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
@@ -14543,22 +14543,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>designjy</t>
+          <t>lha0509</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>01035455888</t>
+          <t>01099215769</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E505" t="inlineStr"/>
@@ -14571,22 +14571,22 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>lha0509</t>
+          <t>designjy</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>01099215769</t>
+          <t>01035455888</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E506" t="inlineStr"/>
@@ -15635,12 +15635,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15663,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -16699,12 +16699,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>likeessay</t>
+          <t>kk_2874121871</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>01087636086</t>
+          <t>01040870367</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E582" t="inlineStr"/>
@@ -16727,12 +16727,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>kk_2874121871</t>
+          <t>likeessay</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>01040870367</t>
+          <t>01087636086</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E583" t="inlineStr"/>
@@ -18099,22 +18099,22 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_5002711068</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01091991969</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E632" t="inlineStr"/>
@@ -18127,12 +18127,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_5002711068</t>
+          <t>kk_4705329623</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01091991969</t>
+          <t>01064926793</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E633" t="inlineStr"/>
@@ -18155,22 +18155,22 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4705329623</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01064926793</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E634" t="inlineStr"/>
@@ -19751,12 +19751,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>kk_4318436675</t>
+          <t>kk_3786745879</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01031176390</t>
+          <t>01093675013</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
@@ -19779,12 +19779,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_3786745879</t>
+          <t>kk_4318436675</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01093675013</t>
+          <t>01031176390</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -20479,12 +20479,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>kk_4202144050</t>
+          <t>kk_4883722134</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01085708380</t>
+          <t>01043573603</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
@@ -20507,12 +20507,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>kk_4883722134</t>
+          <t>kk_4202144050</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01043573603</t>
+          <t>01085708380</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_LIGHTBACKPACK</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E718" t="inlineStr"/>
@@ -20675,22 +20675,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>kk_4588287948</t>
+          <t>cyclepm</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>01091651067</t>
+          <t>01027101838</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_1110_Raffle</t>
         </is>
       </c>
       <c r="E724" t="inlineStr"/>
@@ -20703,22 +20703,22 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>kk_4747397154</t>
+          <t>kk_4588287948</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>01052568046</t>
+          <t>01091651067</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E725" t="inlineStr"/>
@@ -20731,22 +20731,22 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>cyclepm</t>
+          <t>kk_4747397154</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>01027101838</t>
+          <t>01052568046</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>LMS_ECOM_1110_Raffle</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E726" t="inlineStr"/>
@@ -21907,22 +21907,22 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>hunylee</t>
+          <t>silverjida</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01086334375</t>
+          <t>01028180759</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E768" t="inlineStr"/>
@@ -21935,22 +21935,22 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>silverjida</t>
+          <t>hunylee</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01028180759</t>
+          <t>01086334375</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
@@ -23531,22 +23531,22 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>kk_3295287343</t>
+          <t>kk_3691186788</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>01055787714</t>
+          <t>01072030738</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E826" t="inlineStr"/>
@@ -23559,22 +23559,22 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>kk_3691186788</t>
+          <t>kk_3295287343</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01072030738</t>
+          <t>01055787714</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E827" t="inlineStr"/>
@@ -23615,12 +23615,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23643,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -24119,22 +24119,22 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4298043202</t>
+          <t>tesung1133</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01047114486</t>
+          <t>01080018889</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
@@ -24147,22 +24147,22 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tesung1133</t>
+          <t>kk_4298043202</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01080018889</t>
+          <t>01047114486</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -24287,22 +24287,22 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>ohjeong2</t>
+          <t>uok77</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>01034324152</t>
+          <t>01089602950</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
         </is>
       </c>
       <c r="E853" t="inlineStr"/>
@@ -24315,22 +24315,22 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>uok77</t>
+          <t>ohjeong2</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01089602950</t>
+          <t>01034324152</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0507_EFW_STYLE2</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E854" t="inlineStr"/>
@@ -24371,12 +24371,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24399,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24414,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24707,12 +24707,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24735,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -24791,12 +24791,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>kk_4645594639</t>
+          <t>kk_4688432632</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>01076731349</t>
+          <t>01081882909</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -24806,7 +24806,7 @@
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
@@ -24819,12 +24819,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>kk_4688432632</t>
+          <t>kk_4645594639</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01081882909</t>
+          <t>01076731349</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -24834,7 +24834,7 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
@@ -25295,22 +25295,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25323,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25659,12 +25659,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25674,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25687,12 +25687,12 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>jhj95</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01031240827</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -25715,12 +25715,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>jhj95</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01031240827</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1y_target_segments.xlsx
@@ -451,27 +451,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sotank</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>01090171948</t>
-        </is>
-      </c>
+          <t>styleship</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M's Three Rock Jacket</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gbj20022002</t>
+          <t>inhip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01053509041</t>
+          <t>01027705324</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,7 +526,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -543,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>merhen</t>
+          <t>kk_2873136069</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01025129134</t>
+          <t>01048866068</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -571,22 +567,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inhip</t>
+          <t>kk_3864149982</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01027705324</t>
+          <t>01025551942</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -599,22 +595,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_2873136069</t>
+          <t>kk_3433423317</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01048866068</t>
+          <t>01075326556</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -627,22 +623,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_3864149982</t>
+          <t>cool2vs2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01025551942</t>
+          <t>01027216492</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -655,22 +651,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>kk_4293495304</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01032960676</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -683,22 +679,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cool2vs2</t>
+          <t>tjsgksrlf123</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01027216492</t>
+          <t>01033775889</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>EDM_0126_bestreview</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -711,22 +707,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4293495304</t>
+          <t>kk_4446330406</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01032960676</t>
+          <t>01027816365</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -739,12 +735,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tjsgksrlf123</t>
+          <t>magazz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01033775889</t>
+          <t>01099409643</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -754,7 +750,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDM_0126_bestreview</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -767,22 +763,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4446330406</t>
+          <t>kk_4209546622</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01027816365</t>
+          <t>01079193288</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -795,12 +791,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>magazz</t>
+          <t>speedking</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01099409643</t>
+          <t>01051344025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -810,7 +806,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -823,22 +819,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4209546622</t>
+          <t>jhoh55555</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01079193288</t>
+          <t>01062626688</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -851,22 +847,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>speedking</t>
+          <t>hennessy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01051344025</t>
+          <t>01030027773</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -879,22 +875,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jhoh55555</t>
+          <t>kk_3803973742</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01062626688</t>
+          <t>01062581642</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -907,22 +903,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hennessy</t>
+          <t>psw242</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01030027773</t>
+          <t>01054125832</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -935,22 +931,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3803973742</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01062581642</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -963,22 +959,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>psw242</t>
+          <t>kk_4793170858</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01054125832</t>
+          <t>01077026417</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -991,22 +987,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1019,22 +1015,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4793170858</t>
+          <t>arrtieom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01077026417</t>
+          <t>01071593949</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1047,12 +1043,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kk_4778273271</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01029527548</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1062,7 +1058,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1075,12 +1071,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>arrtieom</t>
+          <t>eastrain9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01071593949</t>
+          <t>01071445034</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1090,7 +1086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0521_BAHAMA1</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1103,12 +1099,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4778273271</t>
+          <t>greom73</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01029527548</t>
+          <t>01086372526</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1118,7 +1114,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1131,22 +1127,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eastrain9</t>
+          <t>gidongi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01071445034</t>
+          <t>01064373200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1159,12 +1155,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>kk_4323824634</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01021939477</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1174,7 +1170,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1187,22 +1183,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gidongi</t>
+          <t>skku2738</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01064373200</t>
+          <t>01074152738</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1215,12 +1211,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4323824634</t>
+          <t>chan680</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01021939477</t>
+          <t>01026244284</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1230,7 +1226,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1243,22 +1239,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>skku2738</t>
+          <t>kk_4276234081</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01074152738</t>
+          <t>01046630168</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1271,22 +1267,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chan680</t>
+          <t>jhyeon41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01026244284</t>
+          <t>01038106019</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1299,12 +1295,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4276234081</t>
+          <t>kk_2826785228</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01046630168</t>
+          <t>01022372658</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1314,7 +1310,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1327,22 +1323,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jhyeon41</t>
+          <t>kk_3511421009</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01038106019</t>
+          <t>01031496540</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1355,12 +1351,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_2826785228</t>
+          <t>kk_4806290091</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01022372658</t>
+          <t>01042848444</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1370,7 +1366,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1383,22 +1379,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3511421009</t>
+          <t>serica22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01031496540</t>
+          <t>01095513653</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0705_SEASON_OFF_2ND</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1411,22 +1407,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4806290091</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01042848444</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1439,22 +1435,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>serica22</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01095513653</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0705_SEASON_OFF_2ND</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1467,22 +1463,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>ysc1111</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01041763874</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1495,12 +1491,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1510,7 +1506,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1523,12 +1519,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ysc1111</t>
+          <t>kk_3097873244</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01041763874</t>
+          <t>01032060915</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1538,7 +1534,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1551,12 +1547,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>alonzo22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01062838804</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1566,7 +1562,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1579,22 +1575,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3097873244</t>
+          <t>kk_3746984520</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01032060915</t>
+          <t>01029951804</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1607,12 +1603,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>alonzo22</t>
+          <t>kk_3895206189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01062838804</t>
+          <t>01043980107</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1622,7 +1618,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1635,22 +1631,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3746984520</t>
+          <t>k8017544</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01029951804</t>
+          <t>01095772982</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1663,22 +1659,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_3895206189</t>
+          <t>kk_4745169563</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01043980107</t>
+          <t>01047026526</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1691,22 +1687,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>k8017544</t>
+          <t>djak0712</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01095772982</t>
+          <t>01063559841</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1719,22 +1715,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4745169563</t>
+          <t>gunnie234</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01047026526</t>
+          <t>01099652641</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1747,17 +1743,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>djak0712</t>
+          <t>kk_4946126994</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01063559841</t>
+          <t>01055149084</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1775,22 +1771,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>gunnie234</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01099652641</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1803,12 +1799,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4946126994</t>
+          <t>oshibun</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01055149084</t>
+          <t>01029500259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1818,7 +1814,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1831,22 +1827,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_3042011585</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01073685152</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1859,22 +1855,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oshibun</t>
+          <t>passion1984</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01029500259</t>
+          <t>01064630333</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1887,12 +1883,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3042011585</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01073685152</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1902,7 +1898,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1915,22 +1911,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>passion1984</t>
+          <t>kk_3297935659</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01064630333</t>
+          <t>01090281747</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1943,17 +1939,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_4656100370</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01091056580</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1971,12 +1967,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>kk_3840423259</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01050355480</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1986,7 +1982,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -1999,12 +1995,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4656100370</t>
+          <t>redblood271</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01091056580</t>
+          <t>01031572135</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2014,7 +2010,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2027,12 +2023,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_3840423259</t>
+          <t>kk_5034001705</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01050355480</t>
+          <t>01090601731</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2042,7 +2038,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2055,22 +2051,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>redblood271</t>
+          <t>kk_3224620899</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01031572135</t>
+          <t>01085627400</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2083,22 +2079,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_5034001705</t>
+          <t>kkhgreen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01090601731</t>
+          <t>01092780969</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2111,12 +2107,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3224620899</t>
+          <t>kk_4319428238</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01085627400</t>
+          <t>01092785785</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2126,7 +2122,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2139,12 +2135,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kkhgreen</t>
+          <t>kk_3941500642</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01092780969</t>
+          <t>01074450002</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2154,7 +2150,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2167,12 +2163,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4319428238</t>
+          <t>beki76</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01092785785</t>
+          <t>01088004778</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2195,22 +2191,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3941500642</t>
+          <t>pck490210</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01074450002</t>
+          <t>01025491031</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2223,22 +2219,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>beki76</t>
+          <t>matmata</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01088004778</t>
+          <t>01084207951</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2251,12 +2247,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>pck490210</t>
+          <t>kk_3977151705</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01025491031</t>
+          <t>01025952746</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2266,7 +2262,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2279,12 +2275,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>matmata</t>
+          <t>terran1123</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01084207951</t>
+          <t>01053324395</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2294,7 +2290,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2307,22 +2303,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3977151705</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01025952746</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2335,22 +2331,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>terran1123</t>
+          <t>bbijim</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01053324395</t>
+          <t>01086676776</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2363,12 +2359,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3297492631</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01022470507</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2378,7 +2374,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -2391,22 +2387,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bbijim</t>
+          <t>rudalsla</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01086676776</t>
+          <t>01071949782</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2419,12 +2415,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3297492631</t>
+          <t>cubewheel</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01022470507</t>
+          <t>01089546320</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2434,7 +2430,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2447,22 +2443,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rudalsla</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01071949782</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2475,12 +2471,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cubewheel</t>
+          <t>kk_4991395508</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01089546320</t>
+          <t>01025638959</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2490,7 +2486,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2503,22 +2499,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_2988538598</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01055855280</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2531,22 +2527,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4991395508</t>
+          <t>kk_3180798849</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01025638959</t>
+          <t>01086259207</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2559,22 +2555,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_2988538598</t>
+          <t>kk_3949933982</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01055855280</t>
+          <t>01026968241</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2587,12 +2583,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_3180798849</t>
+          <t>gitae76</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01086259207</t>
+          <t>01020801107</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2615,12 +2611,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3949933982</t>
+          <t>kk_3182573827</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01026968241</t>
+          <t>01077419077</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2630,7 +2626,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2643,12 +2639,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gitae76</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01020801107</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2658,7 +2654,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2671,22 +2667,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3182573827</t>
+          <t>prologic</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01077419077</t>
+          <t>01090864344</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2699,12 +2695,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>kk_4863256269</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01027382913</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2714,7 +2710,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2727,12 +2723,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>prologic</t>
+          <t>insangpa72</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01090864344</t>
+          <t>01053035171</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2742,7 +2738,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2755,12 +2751,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4863256269</t>
+          <t>bjh4895</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01027382913</t>
+          <t>01042374895</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2770,7 +2766,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2783,22 +2779,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>insangpa72</t>
+          <t>kjjopen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01053035171</t>
+          <t>01086035744</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2811,22 +2807,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bjh4895</t>
+          <t>kk_3425319183</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01042374895</t>
+          <t>01073728534</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2839,22 +2835,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kjjopen</t>
+          <t>blackout9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01086035744</t>
+          <t>01054444345</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2867,12 +2863,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3425319183</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01073728534</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2882,7 +2878,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2895,22 +2891,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>blackout9</t>
+          <t>kk_3522301091</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01054444345</t>
+          <t>01088731863</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2923,12 +2919,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2938,7 +2934,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2951,12 +2947,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_3522301091</t>
+          <t>garfield98</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01088731863</t>
+          <t>01032643963</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2966,7 +2962,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2979,12 +2975,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2994,7 +2990,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3007,12 +3003,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>garfield98</t>
+          <t>kk_4355884570</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01032643963</t>
+          <t>01052096279</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3035,22 +3031,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_4785141094</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01022106967</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3063,22 +3059,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4355884570</t>
+          <t>king1090</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01052096279</t>
+          <t>01064003306</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3091,22 +3087,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4785141094</t>
+          <t>mo21613</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01022106967</t>
+          <t>01063041255</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3119,22 +3115,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>king1090</t>
+          <t>johun0414</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01064003306</t>
+          <t>01082150607</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3147,17 +3143,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mo21613</t>
+          <t>kk_4313489248</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01063041255</t>
+          <t>01026591380</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3175,22 +3171,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>johun0414</t>
+          <t>kk_3781116310</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01082150607</t>
+          <t>01052721277</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3203,12 +3199,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4313489248</t>
+          <t>gun9670</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01026591380</t>
+          <t>01051514803</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3231,22 +3227,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3781116310</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01052721277</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3259,12 +3255,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>gun9670</t>
+          <t>kk_3941904586</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01051514803</t>
+          <t>01067078239</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3274,7 +3270,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3287,12 +3283,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_4993751323</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01053138487</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3302,7 +3298,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3315,12 +3311,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_3941904586</t>
+          <t>kk_3478853991</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01067078239</t>
+          <t>01077662474</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3330,7 +3326,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3343,12 +3339,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4993751323</t>
+          <t>kk_3738826876</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01053138487</t>
+          <t>01095514239</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3358,7 +3354,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3371,12 +3367,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3478853991</t>
+          <t>hg1890</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01077662474</t>
+          <t>01038436423</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3386,7 +3382,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3399,12 +3395,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_3738826876</t>
+          <t>hiwoong76</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01095514239</t>
+          <t>01067981478</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3414,7 +3410,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3427,12 +3423,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>hg1890</t>
+          <t>kk_3225675516</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01038436423</t>
+          <t>01022881015</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3442,7 +3438,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>EDM_0226</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -3455,12 +3451,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>hiwoong76</t>
+          <t>nbhfrancisco</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01067981478</t>
+          <t>01050977100</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3470,7 +3466,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3483,12 +3479,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_3225675516</t>
+          <t>kk_4678957107</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01022881015</t>
+          <t>01034388709</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3498,7 +3494,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EDM_0226</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3511,22 +3507,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nbhfrancisco</t>
+          <t>jung03</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01050977100</t>
+          <t>01026209151</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3539,22 +3535,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4678957107</t>
+          <t>yoichi</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01034388709</t>
+          <t>01072692907</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3567,22 +3563,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>jung03</t>
+          <t>kk_3933214484</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01026209151</t>
+          <t>01090832304</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3595,12 +3591,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>yoichi</t>
+          <t>kk_4940441538</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01072692907</t>
+          <t>01089269967</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3610,7 +3606,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3623,12 +3619,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3933214484</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01090832304</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3638,7 +3634,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3651,22 +3647,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4940441538</t>
+          <t>kk_3240277946</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01089269967</t>
+          <t>01049229190</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3679,12 +3675,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_4727133236</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01064755009</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3694,7 +3690,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3707,22 +3703,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3240277946</t>
+          <t>nayuna1022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01049229190</t>
+          <t>01062175214</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3735,12 +3731,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4727133236</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01064755009</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3750,7 +3746,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[PF]전환_신상품 카탈로그(1865,관심사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3763,22 +3759,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nayuna1022</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01062175214</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3791,22 +3787,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>yjookim67</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01054114855</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3819,22 +3815,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>camha</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01031331918</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3847,22 +3843,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>yjookim67</t>
+          <t>dawonint</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01054114855</t>
+          <t>01037690185</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -3875,12 +3871,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>camha</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01031331918</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3890,7 +3886,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3903,22 +3899,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dawonint</t>
+          <t>kk_5008721553</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01037690185</t>
+          <t>01089905677</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3931,22 +3927,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>jswoo99</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01031705383</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3959,22 +3955,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_5008721553</t>
+          <t>kk_3179544090</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01089905677</t>
+          <t>01095352220</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3987,22 +3983,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>jswoo99</t>
+          <t>kk_4796376423</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01031705383</t>
+          <t>01035771357</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -4015,22 +4011,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3179544090</t>
+          <t>kk_3363127172</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01095352220</t>
+          <t>01072739372</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -4043,12 +4039,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4796376423</t>
+          <t>kk_4804817546</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01035771357</t>
+          <t>01048111806</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4058,7 +4054,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -4071,22 +4067,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_3363127172</t>
+          <t>kk_4929674815</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01072739372</t>
+          <t>01075264562</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -4099,22 +4095,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4804817546</t>
+          <t>his9742</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01048111806</t>
+          <t>01024949742</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -4127,22 +4123,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4929674815</t>
+          <t>ils1706</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01075264562</t>
+          <t>01037004519</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -4155,22 +4151,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>his9742</t>
+          <t>kk_3477586140</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01024949742</t>
+          <t>01066698868</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4183,12 +4179,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ils1706</t>
+          <t>jklee1316</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01037004519</t>
+          <t>01023358588</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4198,7 +4194,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -4211,22 +4207,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3477586140</t>
+          <t>kk_3778944759</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01066698868</t>
+          <t>01066975193</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4239,22 +4235,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>jklee1316</t>
+          <t>ino326</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01023358588</t>
+          <t>01024921837</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -4267,12 +4263,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3778944759</t>
+          <t>kk_4378858812_2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01066975193</t>
+          <t>01090939890</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4282,7 +4278,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -4295,22 +4291,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ino326</t>
+          <t>kk_4300806197</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01024921837</t>
+          <t>01045551631</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -4323,12 +4319,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4378858812_2</t>
+          <t>kk_4880545805</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01090939890</t>
+          <t>01022237436</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4338,7 +4334,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_1128_WINTERFESTIVAL_CTA</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -4351,12 +4347,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4300806197</t>
+          <t>by5500</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01045551631</t>
+          <t>01071770101</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4366,7 +4362,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -4379,12 +4375,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4880545805</t>
+          <t>kk_3246810283</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01022237436</t>
+          <t>01039315369</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4394,7 +4390,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -4407,22 +4403,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>by5500</t>
+          <t>show5430</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01071770101</t>
+          <t>01099500131</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4435,22 +4431,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3246810283</t>
+          <t>xcable</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01039315369</t>
+          <t>01080043359</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4463,12 +4459,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>show5430</t>
+          <t>lsu3080</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01099500131</t>
+          <t>01068283080</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4478,7 +4474,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4491,22 +4487,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>xcable</t>
+          <t>kk_2762161146</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01080043359</t>
+          <t>01046533615</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_GnR</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4519,22 +4515,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>lsu3080</t>
+          <t>kk_3212536253</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01068283080</t>
+          <t>01097992453</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4547,12 +4543,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_2762161146</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01046533615</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4562,7 +4558,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_GnR</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -4575,12 +4571,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3212536253</t>
+          <t>policejs</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01097992453</t>
+          <t>01041704743</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4590,7 +4586,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -4603,12 +4599,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>jpm111</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01029304010</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4618,7 +4614,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -4631,22 +4627,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>policejs</t>
+          <t>hajd1011</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01041704743</t>
+          <t>01054401373</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -4659,22 +4655,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jpm111</t>
+          <t>yksik0528</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01029304010</t>
+          <t>01033992431</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4687,22 +4683,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>hajd1011</t>
+          <t>kk_4693581167</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01054401373</t>
+          <t>01050127862</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -4715,22 +4711,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>yksik0528</t>
+          <t>kk_4881694655</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01033992431</t>
+          <t>01072580898</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -4743,22 +4739,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4693581167</t>
+          <t>kk_4702753709</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01050127862</t>
+          <t>01076663512</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4771,12 +4767,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4881694655</t>
+          <t>net1122</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01072580898</t>
+          <t>01040964937</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4786,7 +4782,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4799,12 +4795,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4702753709</t>
+          <t>kk_4927707365</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01076663512</t>
+          <t>01053829303</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4814,7 +4810,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4827,12 +4823,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>net1122</t>
+          <t>koreankim</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01040964937</t>
+          <t>01095372588</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4842,7 +4838,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4855,12 +4851,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4927707365</t>
+          <t>kk_3181446328</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01053829303</t>
+          <t>01086441161</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4870,7 +4866,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4883,12 +4879,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>koreankim</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01095372588</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4911,12 +4907,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_3181446328</t>
+          <t>kk_4360429720</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01086441161</t>
+          <t>01089099036</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4926,7 +4922,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4939,12 +4935,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4954,7 +4950,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4967,12 +4963,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4360429720</t>
+          <t>kk_4703845503</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01089099036</t>
+          <t>01057372401</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4982,7 +4978,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4995,12 +4991,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_3763845552</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01095701533</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5010,7 +5006,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5023,22 +5019,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4703845503</t>
+          <t>luvieye123</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01057372401</t>
+          <t>01035949045</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5051,22 +5047,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_3763845552</t>
+          <t>pooo1228</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01095701533</t>
+          <t>01062724056</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -5079,22 +5075,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>luvieye123</t>
+          <t>kk_3380720822</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01035949045</t>
+          <t>01054705220</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -5107,12 +5103,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>pooo1228</t>
+          <t>kk_3305072060</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01062724056</t>
+          <t>01085390140</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5122,7 +5118,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -5135,12 +5131,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3380720822</t>
+          <t>kk_4409064497</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01054705220</t>
+          <t>01057371727</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5150,7 +5146,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -5163,12 +5159,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_3305072060</t>
+          <t>kk_4430409947</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01085390140</t>
+          <t>01047358234</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5178,7 +5174,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,논타겟)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -5191,22 +5187,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4409064497</t>
+          <t>lefy</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01057371727</t>
+          <t>01022414020</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -5219,22 +5215,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4430409947</t>
+          <t>varkala1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01047358234</t>
+          <t>01080276669</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -5247,22 +5243,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>lefy</t>
+          <t>njp0710</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01022414020</t>
+          <t>01027282087</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>0610</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -5275,12 +5271,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>varkala1</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01080276669</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5303,12 +5299,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>njp0710</t>
+          <t>cshc</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01027282087</t>
+          <t>01053437643</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5318,7 +5314,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0610</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5331,22 +5327,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>thebebob</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01094365308</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5359,12 +5355,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cshc</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01053437643</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5374,7 +5370,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5387,22 +5383,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>thebebob</t>
+          <t>fkilove</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01094365308</t>
+          <t>01080118915</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -5415,12 +5411,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>ace1331</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01033906903</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5430,7 +5426,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0502</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5443,12 +5439,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ace1331</t>
+          <t>zxcvziii</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01033906903</t>
+          <t>01048169121</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5458,7 +5454,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EDM_0502</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5471,12 +5467,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>fkilove</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01080118915</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5486,7 +5482,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -5499,12 +5495,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>zxcvziii</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01048169121</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5514,7 +5510,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5527,22 +5523,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>kk_4461497985</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01063241461</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5555,12 +5551,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_4739241016</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01082593038</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5570,7 +5566,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5583,22 +5579,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4461497985</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01063241461</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -5611,22 +5607,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4739241016</t>
+          <t>ckddus2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01082593038</t>
+          <t>01048722142</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>MOhomelink</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -5639,12 +5635,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>juks2761</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01062646133</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5654,7 +5650,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0129</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -5667,12 +5663,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ckddus2</t>
+          <t>kk_4659940912</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01048722142</t>
+          <t>01041612810</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5682,7 +5678,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>MOhomelink</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -5695,12 +5691,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>juks2761</t>
+          <t>jyjangcti</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01062646133</t>
+          <t>01029378908</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5710,7 +5706,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0129</t>
+          <t>EDM_0512</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -5723,22 +5719,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4659940912</t>
+          <t>rao2001</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01041612810</t>
+          <t>01025653293</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -5751,22 +5747,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>jyjangcti</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01029378908</t>
+          <t>01063315178</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>EDM_0512</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -5779,12 +5775,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rao2001</t>
+          <t>bong9ya</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01025653293</t>
+          <t>01045637364</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5794,7 +5790,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -5807,12 +5803,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>lcs3017</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01063315178</t>
+          <t>01094123017</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5822,7 +5818,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -5835,12 +5831,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>bong9ya</t>
+          <t>ljw855</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01045637364</t>
+          <t>01041724332</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5850,7 +5846,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -5863,22 +5859,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>lcs3017</t>
+          <t>amistrong</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01094123017</t>
+          <t>01055097870</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -5891,22 +5887,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ljw855</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01041724332</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -5919,22 +5915,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>amistrong</t>
+          <t>kk_4711669963</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01055097870</t>
+          <t>01053480904</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5947,22 +5943,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>boxyogo</t>
+          <t>kk_3626975387</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01047175275</t>
+          <t>01088796035</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -5975,22 +5971,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4711669963</t>
+          <t>kk_3100841256</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01053480904</t>
+          <t>01054473961</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -6003,12 +5999,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_3626975387</t>
+          <t>kk_4339204533</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01088796035</t>
+          <t>01064869716</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6018,7 +6014,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -6031,12 +6027,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_3100841256</t>
+          <t>kk_4826700021</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01054473961</t>
+          <t>01066078107</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6046,7 +6042,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -6059,12 +6055,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4339204533</t>
+          <t>kk_4240554258</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01064869716</t>
+          <t>01035989843</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6074,7 +6070,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -6087,22 +6083,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4826700021</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01066078107</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -6115,22 +6111,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_4240554258</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01035989843</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -6143,12 +6139,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>dimejin</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01086058650</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6158,7 +6154,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -6171,12 +6167,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kjh30201236</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01030204946</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6186,7 +6182,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -6199,12 +6195,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>dimejin</t>
+          <t>kk_2847176143</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01086058650</t>
+          <t>01038261331</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6227,12 +6223,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kjh30201236</t>
+          <t>kk_3170960220</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01030204946</t>
+          <t>01087729278</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6242,7 +6238,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6255,22 +6251,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_2847176143</t>
+          <t>kk_4748122429</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01038261331</t>
+          <t>01089229240</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6283,22 +6279,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_3170960220</t>
+          <t>kk_4545437798</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01087729278</t>
+          <t>01021996968</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -6311,22 +6307,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4748122429</t>
+          <t>kk_3728489315</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01089229240</t>
+          <t>01088859514</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -6339,22 +6335,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_4545437798</t>
+          <t>nexen1974a</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01021996968</t>
+          <t>01055782215</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -6367,22 +6363,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_3728489315</t>
+          <t>kk_4648812045</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01088859514</t>
+          <t>01045190963</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -6395,17 +6391,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>nexen1974a</t>
+          <t>kk_3621695729</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01055782215</t>
+          <t>01053495037</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6423,12 +6419,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_4648812045</t>
+          <t>kk_4789987921</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01045190963</t>
+          <t>01053009139</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6438,7 +6434,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6451,12 +6447,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_3621695729</t>
+          <t>lov2jjin</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01053495037</t>
+          <t>01087038707</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6466,7 +6462,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -6479,12 +6475,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4789987921</t>
+          <t>jakelee</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01053009139</t>
+          <t>01027223531</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6494,7 +6490,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -6507,12 +6503,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>lov2jjin</t>
+          <t>kk_4391641739</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01087038707</t>
+          <t>01091994491</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6535,12 +6531,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>jakelee</t>
+          <t>kk_2873620176</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01027223531</t>
+          <t>01029480082</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6550,7 +6546,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -6563,12 +6559,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4391641739</t>
+          <t>kk_4660550146</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01091994491</t>
+          <t>01022238698</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6578,7 +6574,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -6591,22 +6587,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_2873620176</t>
+          <t>kji5472</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01029480082</t>
+          <t>01022054672</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -6619,12 +6615,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_4660550146</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01022238698</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6634,7 +6630,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -6647,12 +6643,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kji5472</t>
+          <t>kk_3260158755</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01022054672</t>
+          <t>01038984931</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6675,12 +6671,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>shon5072</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01095777956</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6690,7 +6686,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -6703,22 +6699,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_3260158755</t>
+          <t>mijlove</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01038984931</t>
+          <t>01092285002</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -6731,22 +6727,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>shon5072</t>
+          <t>nicole</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01095777956</t>
+          <t>01083410822</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>pmax</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -6759,22 +6755,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>mijlove</t>
+          <t>yahoo0402</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01092285002</t>
+          <t>01050319361</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -6787,22 +6783,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>nicole</t>
+          <t>kk_4848752733</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01083410822</t>
+          <t>01090534422</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -6815,22 +6811,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>yahoo0402</t>
+          <t>kk_4825328334</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01050319361</t>
+          <t>01022625558</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -6843,12 +6839,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_4848752733</t>
+          <t>kk_4711817746</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01090534422</t>
+          <t>01073740979</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6858,7 +6854,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -6871,22 +6867,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_4825328334</t>
+          <t>kk_3914085758</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01022625558</t>
+          <t>01031872338</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -6899,12 +6895,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4711817746</t>
+          <t>kk_4896487866</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01073740979</t>
+          <t>01050400311</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6914,7 +6910,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -6927,12 +6923,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3914085758</t>
+          <t>kk_3227570959</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01031872338</t>
+          <t>01028169084</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6942,7 +6938,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -6955,12 +6951,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4896487866</t>
+          <t>segyung2</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01050400311</t>
+          <t>01089808520</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6970,7 +6966,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -6983,22 +6979,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_3227570959</t>
+          <t>sclpion</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01028169084</t>
+          <t>01088740653</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7011,12 +7007,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>segyung2</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01089808520</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7026,7 +7022,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7039,12 +7035,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sclpion</t>
+          <t>kk_3607933321</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01088740653</t>
+          <t>01035122820</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7054,7 +7050,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7067,22 +7063,22 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4481949959</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01077434037</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7095,12 +7091,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_3607933321</t>
+          <t>kk_4860720956</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01035122820</t>
+          <t>01056709617</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7110,7 +7106,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자30일)</t>
+          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7123,12 +7119,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4481949959</t>
+          <t>kk_4467979962</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01077434037</t>
+          <t>01037751563</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7138,7 +7134,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7151,12 +7147,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_4860720956</t>
+          <t>kk_2770056564</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01056709617</t>
+          <t>01097609451</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7166,7 +7162,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0423_EFW</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7179,12 +7175,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4467979962</t>
+          <t>kk_5009517640</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01037751563</t>
+          <t>01090817520</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7194,7 +7190,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>방문_하이브리드 오디언스</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7207,22 +7203,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_5009517640</t>
+          <t>ryeol1004</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01090817520</t>
+          <t>01087308928</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>방문_하이브리드 오디언스</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7235,12 +7231,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_2770056564</t>
+          <t>chk1987</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01097609451</t>
+          <t>01067608088</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7250,7 +7246,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7263,22 +7259,22 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ryeol1004</t>
+          <t>kk_4520208596</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01087308928</t>
+          <t>01025741462</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -7291,22 +7287,22 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>chk1987</t>
+          <t>kk_3182043466</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01067608088</t>
+          <t>01092562936</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -7319,22 +7315,22 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_4520208596</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01025741462</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -7347,22 +7343,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kk_3182043466</t>
+          <t>pearl52</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01092562936</t>
+          <t>01050351018</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -7375,22 +7371,22 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4929043811</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01037904341</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -7403,12 +7399,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>pearl52</t>
+          <t>kk_4673119425</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01050351018</t>
+          <t>01085632266</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7418,7 +7414,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naversa_pc</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -7431,12 +7427,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_4929043811</t>
+          <t>kk_3639045388</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01037904341</t>
+          <t>01064334743</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7446,7 +7442,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -7459,12 +7455,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_4673119425</t>
+          <t>gbj20022002</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01085632266</t>
+          <t>01053509041</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7474,7 +7470,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -7487,22 +7483,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_3639045388</t>
+          <t>kk_4744667185</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01064334743</t>
+          <t>01047226521</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -7515,22 +7511,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4744667185</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01047226521</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -7543,22 +7539,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3337408762</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01095768922</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -7571,22 +7567,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_3337408762</t>
+          <t>kk_4650374928</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01095768922</t>
+          <t>01086157107</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -7599,22 +7595,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kk_4650374928</t>
+          <t>kk_3388290079</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01086157107</t>
+          <t>01083191557</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>kakao_ch_message_0325_s26new_cta</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -7627,12 +7623,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_3388290079</t>
+          <t>ysj1127</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01083191557</t>
+          <t>01071109388</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7642,7 +7638,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>kakao_ch_message_0325_s26new_cta</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -7655,12 +7651,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ysj1127</t>
+          <t>pyhlove53</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01071109388</t>
+          <t>01094031004</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7670,7 +7666,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -7683,22 +7679,22 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>pyhlove53</t>
+          <t>honor181</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01094031004</t>
+          <t>01046301211</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -7711,12 +7707,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>honor181</t>
+          <t>ddolme</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01046301211</t>
+          <t>01050040644</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7726,7 +7722,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -7739,22 +7735,22 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ddolme</t>
+          <t>kk_4416125651</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01050040644</t>
+          <t>01052177552</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -7767,22 +7763,22 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4416125651</t>
+          <t>bbjj2000</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01052177552</t>
+          <t>01035218300</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -7795,22 +7791,22 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>bbjj2000</t>
+          <t>sih92</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01035218300</t>
+          <t>01029623377</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -7823,22 +7819,22 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>sih92</t>
+          <t>kk_3835565251</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01029623377</t>
+          <t>01027409786</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -7851,12 +7847,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kk_3835565251</t>
+          <t>kingjo</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01027409786</t>
+          <t>01062660099</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7866,7 +7862,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -7879,12 +7875,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kingjo</t>
+          <t>guswo7310</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01062660099</t>
+          <t>01044712040</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7894,7 +7890,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -7907,22 +7903,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>guswo7310</t>
+          <t>kk_2807327385</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01044712040</t>
+          <t>01038584194</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -7935,22 +7931,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_2807327385</t>
+          <t>kk_3639576029</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01038584194</t>
+          <t>01063967727</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -7963,22 +7959,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_3639576029</t>
+          <t>kk_4936216487</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01063967727</t>
+          <t>01045751707</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -7991,12 +7987,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_4936216487</t>
+          <t>pivy87</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01045751707</t>
+          <t>01063819999</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8006,7 +8002,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -8019,12 +8015,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>pivy87</t>
+          <t>kk_2826668268</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01063819999</t>
+          <t>01074843858</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8034,7 +8030,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -8047,17 +8043,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_2826668268</t>
+          <t>joontak</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01074843858</t>
+          <t>01088917848</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8075,22 +8071,22 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>joontak</t>
+          <t>kk_4635961106</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01088917848</t>
+          <t>01027884773</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -8103,22 +8099,22 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4635961106</t>
+          <t>kk_3949518630</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01027884773</t>
+          <t>01033587883</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -8131,12 +8127,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_3949518630</t>
+          <t>hyundoart</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01033587883</t>
+          <t>01096853214</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8146,7 +8142,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -8159,12 +8155,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>hyundoart</t>
+          <t>kk_4600202212</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01096853214</t>
+          <t>01095679374</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8174,7 +8170,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -8187,22 +8183,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4600202212</t>
+          <t>kk_4503210270</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01095679374</t>
+          <t>01071098993</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_WOMEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -8215,12 +8211,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4503210270</t>
+          <t>kk_4481940140</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01071098993</t>
+          <t>01065676272</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8230,7 +8226,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF_SA] 컬럼비아 상시</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -8243,12 +8239,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_4481940140</t>
+          <t>kk_4750629166</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01065676272</t>
+          <t>01065748515</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8258,7 +8254,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>[PF_SA] 컬럼비아 상시</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -8271,22 +8267,22 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4750629166</t>
+          <t>kk_4746271433</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01065748515</t>
+          <t>01088977839</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -8299,12 +8295,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_4746271433</t>
+          <t>mondora</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01088977839</t>
+          <t>01026379832</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8314,7 +8310,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>EDM_0305</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -8327,22 +8323,22 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>mondora</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01026379832</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>EDM_0305</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -8355,22 +8351,22 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>kk_4869187470</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01064823221</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -8383,22 +8379,22 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_4869187470</t>
+          <t>kk_3722415174</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01064823221</t>
+          <t>01036589994</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -8411,12 +8407,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_3722415174</t>
+          <t>loxolist</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01036589994</t>
+          <t>01068552419</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8426,7 +8422,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -8439,22 +8435,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>loxolist</t>
+          <t>oh8314</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01068552419</t>
+          <t>01090595921</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>lf</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -8467,22 +8463,22 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>oh8314</t>
+          <t>kk_3825664300</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01090595921</t>
+          <t>01040323452</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>lf</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -8495,22 +8491,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>kk_3825664300</t>
+          <t>ustar777</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01040323452</t>
+          <t>01027424281</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -8523,22 +8519,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ustar777</t>
+          <t>cjonghak</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01027424281</t>
+          <t>01090444081</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8551,22 +8547,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>cjonghak</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01090444081</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -8579,12 +8575,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>merhen</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01025129134</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8594,7 +8590,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -11603,22 +11599,22 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>aurora1530</t>
+          <t>jaeho86</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>01090756922</t>
+          <t>01091199057</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0317</t>
         </is>
       </c>
       <c r="E400" t="inlineStr"/>
@@ -11631,22 +11627,22 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>jaeho86</t>
+          <t>aurora1530</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>01091199057</t>
+          <t>01090756922</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>EDM_0317</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E401" t="inlineStr"/>
@@ -13087,12 +13083,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ahnnavy</t>
+          <t>kk_4305225948</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>01045624300</t>
+          <t>01097745190</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13102,7 +13098,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -13115,12 +13111,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>kk_4305225948</t>
+          <t>ahnnavy</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>01097745190</t>
+          <t>01045624300</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -13130,7 +13126,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -13507,12 +13503,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_3866704464</t>
+          <t>kk_3377297415</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01096848789</t>
+          <t>01088479524</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13522,7 +13518,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -13535,12 +13531,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kk_3377297415</t>
+          <t>kk_3866704464</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01088479524</t>
+          <t>01096848789</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -13550,7 +13546,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E469" t="inlineStr"/>
@@ -14319,12 +14315,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>kk_4850097780</t>
+          <t>kk_3846090083</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>01053956505</t>
+          <t>01062091126</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -14334,7 +14330,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
@@ -14347,12 +14343,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>kk_3846090083</t>
+          <t>kk_4850097780</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>01062091126</t>
+          <t>01053956505</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -14362,7 +14358,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
@@ -14767,12 +14763,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>kk_3333111023</t>
+          <t>starpos9</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>01046548483</t>
+          <t>01086475152</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14795,12 +14791,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>starpos9</t>
+          <t>kk_3333111023</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>01086475152</t>
+          <t>01046548483</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -15635,12 +15631,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>youl29</t>
+          <t>kk_4602095632</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>01050134121</t>
+          <t>01033213747</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15663,12 +15659,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>kk_4602095632</t>
+          <t>youl29</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>01033213747</t>
+          <t>01050134121</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19947,12 +19943,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4725433749</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01096687926</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -19962,7 +19958,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E698" t="inlineStr"/>
@@ -19975,12 +19971,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>kk_4725433749</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01096687926</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -19990,7 +19986,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
@@ -20675,22 +20671,22 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>cyclepm</t>
+          <t>kk_4747397154</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>01027101838</t>
+          <t>01052568046</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>LMS_ECOM_1110_Raffle</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E724" t="inlineStr"/>
@@ -20731,22 +20727,22 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>kk_4747397154</t>
+          <t>cyclepm</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>01052568046</t>
+          <t>01027101838</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_1110_Raffle</t>
         </is>
       </c>
       <c r="E726" t="inlineStr"/>
@@ -22103,22 +22099,22 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>lovelybeib</t>
+          <t>kk_4857948457</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01040981902</t>
+          <t>01058380760</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
@@ -22131,22 +22127,22 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_4857948457</t>
+          <t>lovelybeib</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01058380760</t>
+          <t>01040981902</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
@@ -22411,12 +22407,12 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>sephira</t>
+          <t>jokowoo</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01041867593</t>
+          <t>01040299924</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -22426,7 +22422,7 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
@@ -22439,12 +22435,12 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>jokowoo</t>
+          <t>sephira</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01040299924</t>
+          <t>01041867593</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -22454,7 +22450,7 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E787" t="inlineStr"/>
@@ -23615,12 +23611,12 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_4582648301</t>
+          <t>kk_3179837389</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01040451815</t>
+          <t>01089490421</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -23630,7 +23626,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>0803_SUMMER_LAST_CHANCE</t>
         </is>
       </c>
       <c r="E829" t="inlineStr"/>
@@ -23643,12 +23639,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>kk_3179837389</t>
+          <t>kk_4582648301</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>01089490421</t>
+          <t>01040451815</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -23658,7 +23654,7 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>0803_SUMMER_LAST_CHANCE</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E830" t="inlineStr"/>
@@ -24371,12 +24367,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>kk_4354536465</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>01090782401</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -24386,7 +24382,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
       <c r="E856" t="inlineStr"/>
@@ -24399,12 +24395,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4354536465</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01090782401</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -24414,7 +24410,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E857" t="inlineStr"/>
@@ -24623,22 +24619,22 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_2771972168</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01029820030</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
@@ -24651,22 +24647,22 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>kk_2771972168</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01029820030</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E866" t="inlineStr"/>
@@ -24707,12 +24703,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3166693744</t>
+          <t>kk_3809928726</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01045579380</t>
+          <t>01079193871</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -24735,12 +24731,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_3166693744</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01045579380</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -25099,12 +25095,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>kk_2957728349</t>
+          <t>kk_4588831805</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>01055754855</t>
+          <t>01062739098</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -25114,7 +25110,7 @@
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E882" t="inlineStr"/>
@@ -25127,12 +25123,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>kk_4588831805</t>
+          <t>kk_2957728349</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>01062739098</t>
+          <t>01055754855</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -25142,7 +25138,7 @@
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E883" t="inlineStr"/>
@@ -25295,22 +25291,22 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_3421258407</t>
+          <t>pavilecolumbia</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01040887568</t>
+          <t>01052876062</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -25323,22 +25319,22 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>pavilecolumbia</t>
+          <t>kk_3421258407</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01052876062</t>
+          <t>01040887568</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -25631,12 +25627,12 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_3957117484</t>
+          <t>khyoon99</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01042204013</t>
+          <t>01044153686</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -25646,7 +25642,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>0520</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E901" t="inlineStr"/>
@@ -25659,12 +25655,12 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>khyoon99</t>
+          <t>kk_2825498802</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01044153686</t>
+          <t>01027817891</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -25674,7 +25670,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E902" t="inlineStr"/>
@@ -25715,12 +25711,12 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>kk_2825498802</t>
+          <t>kk_3957117484</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01027817891</t>
+          <t>01042204013</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -25730,7 +25726,7 @@
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>0520</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>
